--- a/campaign/2026-q4-home-checkup/Bwell_Q4-2026_Home-Checkup_Content-Calendar.xlsx
+++ b/campaign/2026-q4-home-checkup/Bwell_Q4-2026_Home-Checkup_Content-Calendar.xlsx
@@ -16,7 +16,7 @@
     <sheet name="Dependencies" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Calendar'!$A$1:$P$64</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Calendar'!$A$1:$P$79</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -531,7 +531,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B25"/>
+  <dimension ref="A1:B26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -714,72 +714,84 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr"/>
-      <c r="B19" s="3" t="inlineStr"/>
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Seasonal (ผูกฤดูกาล)</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="A20" s="2" t="inlineStr"/>
+      <c r="B20" s="3" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>วิธีใช้</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>ช่องสีเหลือง</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>ช่องที่ทีมต้องกรอก: Owner, Publish date, Status ในชีท Calendar และ Owner ในชีท Dependencies</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>เลือกจาก dropdown: Not started / Briefed / In production / Approved / Published</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>[ ]</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Placeholder ที่ต้องเติม (offer, threshold, interval, KPI) ห้ามใส่ตัวเลขเองโดยไม่ได้รับ confirm</t>
+          <t>เลือกจาก dropdown: Not started / Briefed / In production / Approved / Published</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>แถวตัวอย่าง</t>
+          <t>[ ]</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Calendar แถวแรก (W1) กรอกตัวอย่างไว้ให้ดูรูปแบบ แก้ทับได้เลย</t>
+          <t>Placeholder ที่ต้องเติม (offer, threshold, interval, KPI) ห้ามใส่ตัวเลขเองโดยไม่ได้รับ confirm</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>แถวตัวอย่าง</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Calendar แถวแรก (W1) กรอกตัวอย่างไว้ให้ดูรูปแบบ แก้ทับได้เลย</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
           <t>Source รุ่นสินค้า</t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B26" s="3" t="inlineStr">
         <is>
           <t>Lineup และพื้นที่ ตร.ม. มาจาก staging website (website-review/bwell-nav-prototype.html) ต้องยืนยันกับ stock จริงก่อนใช้</t>
         </is>
@@ -796,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P64"/>
+  <dimension ref="A1:P79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1671,32 +1683,32 @@
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>S</t>
         </is>
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>LINE OA broadcast</t>
+          <t>Seasonal (ผูกฤดูกาล)</t>
         </is>
       </c>
       <c r="I12" s="7" t="inlineStr">
         <is>
-          <t>LINE OA</t>
+          <t>TikTok / IG</t>
         </is>
       </c>
       <c r="J12" s="7" t="inlineStr">
         <is>
-          <t>Cross-category</t>
+          <t>Dehumidifier</t>
         </is>
       </c>
       <c r="K12" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>BDH-12A / 30A / 53A</t>
         </is>
       </c>
       <c r="L12" s="7" t="inlineStr">
         <is>
-          <t>Quiz reminder (คนที่เริ่มแล้วแต่ยังไม่จบ)</t>
+          <t>[ปลายฝน] เช็กลิสต์ 3 จุดในบ้านที่ชื้นที่สุดหลังฝนตก: "ฝนหยุดแล้ว แต่บ้านยังไม่แห้ง"</t>
         </is>
       </c>
       <c r="M12" s="8" t="n"/>
@@ -1706,17 +1718,21 @@
           <t>Not started</t>
         </is>
       </c>
-      <c r="P12" s="7" t="inlineStr"/>
+      <c r="P12" s="7" t="inlineStr">
+        <is>
+          <t>13 ต.ค. งดโพสขายและ content สนุก ปรับ tone ให้สุภาพ</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>W4</t>
+          <t>W3</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>19-25 ต.ค.</t>
+          <t>12-18 ต.ค.</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
@@ -1731,42 +1747,42 @@
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>Body: บ้านควรช่วยให้ร่างกายพัก</t>
+          <t>Clean: ฝุ่นที่มองไม่เห็น</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>ห้องทำงาน / ห้องนอน</t>
+          <t>ห้องนอน / ตู้เสื้อผ้า</t>
         </is>
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>S</t>
         </is>
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
-          <t>Short video (hook 3 วิ)</t>
+          <t>Seasonal (ผูกฤดูกาล)</t>
         </is>
       </c>
       <c r="I13" s="7" t="inlineStr">
         <is>
-          <t>TikTok / Lemon8</t>
+          <t>TikTok / Reels</t>
         </is>
       </c>
       <c r="J13" s="7" t="inlineStr">
         <is>
-          <t>Ergonomic chair</t>
+          <t>Robot vacuum</t>
         </is>
       </c>
       <c r="K13" s="7" t="inlineStr">
         <is>
-          <t>Bjorn / Stella / Astrid / Agnes</t>
+          <t>L6C / L0 / Y1</t>
         </is>
       </c>
       <c r="L13" s="7" t="inlineStr">
         <is>
-          <t>"นั่งแบบนี้มาทั้งปี หลังคุณจะเป็นยังไง" (office syndrome check)</t>
+          <t>[ปลายฝน] ฝุ่นและคราบดินจากรองเท้าเปียก: "รองเท้าเปียกเดินเข้าบ้านกี่รอบต่อวัน"</t>
         </is>
       </c>
       <c r="M13" s="8" t="n"/>
@@ -1778,19 +1794,19 @@
       </c>
       <c r="P13" s="7" t="inlineStr">
         <is>
-          <t>23 ต.ค. วันหยุดยาว: content "วันหยุดจัดบ้านใหม่"</t>
+          <t>13 ต.ค. งดโพสขายและ content สนุก ปรับ tone ให้สุภาพ</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>W4</t>
+          <t>W3</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>19-25 ต.ค.</t>
+          <t>12-18 ต.ค.</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
@@ -1805,42 +1821,42 @@
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>Body: บ้านควรช่วยให้ร่างกายพัก</t>
+          <t>Clean: ฝุ่นที่มองไม่เห็น</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>ห้องทำงาน / ห้องนอน</t>
+          <t>ห้องนอน / ตู้เสื้อผ้า</t>
         </is>
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>E</t>
         </is>
       </c>
       <c r="H14" s="7" t="inlineStr">
         <is>
-          <t>Education / Explainer</t>
+          <t>LINE OA broadcast</t>
         </is>
       </c>
       <c r="I14" s="7" t="inlineStr">
         <is>
-          <t>FB / IG</t>
+          <t>LINE OA</t>
         </is>
       </c>
       <c r="J14" s="7" t="inlineStr">
         <is>
-          <t>Health pillow</t>
+          <t>Cross-category</t>
         </is>
       </c>
       <c r="K14" s="7" t="inlineStr">
         <is>
-          <t>หมอนรองคอเพื่อสุขภาพ</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L14" s="7" t="inlineStr">
         <is>
-          <t>"ตื่นมาปวดคอ อาจเป็นเพราะหมอน"</t>
+          <t>Quiz reminder (คนที่เริ่มแล้วแต่ยังไม่จบ)</t>
         </is>
       </c>
       <c r="M14" s="8" t="n"/>
@@ -1850,11 +1866,7 @@
           <t>Not started</t>
         </is>
       </c>
-      <c r="P14" s="7" t="inlineStr">
-        <is>
-          <t>23 ต.ค. วันหยุดยาว: content "วันหยุดจัดบ้านใหม่"</t>
-        </is>
-      </c>
+      <c r="P14" s="7" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
@@ -1889,32 +1901,32 @@
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H15" s="7" t="inlineStr">
         <is>
-          <t>Engagement (poll / quiz CTA / Q&amp;A)</t>
+          <t>Short video (hook 3 วิ)</t>
         </is>
       </c>
       <c r="I15" s="7" t="inlineStr">
         <is>
-          <t>IG Stories</t>
+          <t>TikTok / Lemon8</t>
         </is>
       </c>
       <c r="J15" s="7" t="inlineStr">
         <is>
-          <t>Health pillow</t>
+          <t>Ergonomic chair</t>
         </is>
       </c>
       <c r="K15" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Bjorn / Stella / Astrid / Agnes</t>
         </is>
       </c>
       <c r="L15" s="7" t="inlineStr">
         <is>
-          <t>Sleep check poll</t>
+          <t>"นั่งแบบนี้มาทั้งปี หลังคุณจะเป็นยังไง" (office syndrome check)</t>
         </is>
       </c>
       <c r="M15" s="8" t="n"/>
@@ -1963,32 +1975,32 @@
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H16" s="7" t="inlineStr">
         <is>
-          <t>LINE OA broadcast</t>
+          <t>Education / Explainer</t>
         </is>
       </c>
       <c r="I16" s="7" t="inlineStr">
         <is>
-          <t>LINE OA</t>
+          <t>FB / IG</t>
         </is>
       </c>
       <c r="J16" s="7" t="inlineStr">
         <is>
-          <t>Cross-category</t>
+          <t>Health pillow</t>
         </is>
       </c>
       <c r="K16" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>หมอนรองคอเพื่อสุขภาพ</t>
         </is>
       </c>
       <c r="L16" s="7" t="inlineStr">
         <is>
-          <t>Mini sleep check ใน chat</t>
+          <t>"ตื่นมาปวดคอ อาจเป็นเพราะหมอน"</t>
         </is>
       </c>
       <c r="M16" s="8" t="n"/>
@@ -1998,17 +2010,21 @@
           <t>Not started</t>
         </is>
       </c>
-      <c r="P16" s="7" t="inlineStr"/>
+      <c r="P16" s="7" t="inlineStr">
+        <is>
+          <t>23 ต.ค. วันหยุดยาว: content "วันหยุดจัดบ้านใหม่"</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>W5</t>
+          <t>W4</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>26 ต.ค.-1 พ.ย.</t>
+          <t>19-25 ต.ค.</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
@@ -2023,42 +2039,42 @@
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>Breathe + Drink</t>
+          <t>Body: บ้านควรช่วยให้ร่างกายพัก</t>
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>ห้องนั่งเล่น / ห้องครัว</t>
+          <t>ห้องทำงาน / ห้องนอน</t>
         </is>
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>D</t>
         </is>
       </c>
       <c r="H17" s="7" t="inlineStr">
         <is>
-          <t>Short video (hook 3 วิ)</t>
+          <t>Engagement (poll / quiz CTA / Q&amp;A)</t>
         </is>
       </c>
       <c r="I17" s="7" t="inlineStr">
         <is>
-          <t>TikTok / Reels</t>
+          <t>IG Stories</t>
         </is>
       </c>
       <c r="J17" s="7" t="inlineStr">
         <is>
-          <t>Air purifier</t>
+          <t>Health pillow</t>
         </is>
       </c>
       <c r="K17" s="7" t="inlineStr">
         <is>
-          <t>AP-H3029US</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L17" s="7" t="inlineStr">
         <is>
-          <t>"ปิดหน้าต่างแล้วฝุ่นในบ้านลดจริงไหม ลองวัดให้ดู" (ห้องนั่งเล่น 40–80 ตร.ม.)</t>
+          <t>Sleep check poll</t>
         </is>
       </c>
       <c r="M17" s="8" t="n"/>
@@ -2070,19 +2086,19 @@
       </c>
       <c r="P17" s="7" t="inlineStr">
         <is>
-          <t>เตรียมเข้าฤดูฝุ่น PM2.5</t>
+          <t>23 ต.ค. วันหยุดยาว: content "วันหยุดจัดบ้านใหม่"</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>W5</t>
+          <t>W4</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>26 ต.ค.-1 พ.ย.</t>
+          <t>19-25 ต.ค.</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
@@ -2097,42 +2113,42 @@
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>Breathe + Drink</t>
+          <t>Body: บ้านควรช่วยให้ร่างกายพัก</t>
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>ห้องนั่งเล่น / ห้องครัว</t>
+          <t>ห้องทำงาน / ห้องนอน</t>
         </is>
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>S</t>
         </is>
       </c>
       <c r="H18" s="7" t="inlineStr">
         <is>
-          <t>Short video (hook 3 วิ)</t>
+          <t>Seasonal (ผูกฤดูกาล)</t>
         </is>
       </c>
       <c r="I18" s="7" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>FB / Lemon8</t>
         </is>
       </c>
       <c r="J18" s="7" t="inlineStr">
         <is>
-          <t>Water purifier</t>
+          <t>Dehumidifier</t>
         </is>
       </c>
       <c r="K18" s="7" t="inlineStr">
         <is>
-          <t>RO แบบไร้ถัง / BW-D103</t>
+          <t>BDH-30A</t>
         </is>
       </c>
       <c r="L18" s="7" t="inlineStr">
         <is>
-          <t>"น้ำที่คุณดื่มที่บ้าน ผ่านอะไรมาบ้าง"</t>
+          <t>[ปลายฝน] ตากผ้าในห้องช่วงฝนตกติดกัน: "ผ้าไม่แห้ง กลิ่นอับตามมา"</t>
         </is>
       </c>
       <c r="M18" s="8" t="n"/>
@@ -2144,19 +2160,19 @@
       </c>
       <c r="P18" s="7" t="inlineStr">
         <is>
-          <t>เตรียมเข้าฤดูฝุ่น PM2.5</t>
+          <t>23 ต.ค. วันหยุดยาว: content "วันหยุดจัดบ้านใหม่"</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>W5</t>
+          <t>W4</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>26 ต.ค.-1 พ.ย.</t>
+          <t>19-25 ต.ค.</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
@@ -2171,42 +2187,42 @@
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>Breathe + Drink</t>
+          <t>Body: บ้านควรช่วยให้ร่างกายพัก</t>
         </is>
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>ห้องนั่งเล่น / ห้องครัว</t>
+          <t>ห้องทำงาน / ห้องนอน</t>
         </is>
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="H19" s="7" t="inlineStr">
         <is>
-          <t>Education / Explainer</t>
+          <t>Seasonal (ผูกฤดูกาล)</t>
         </is>
       </c>
       <c r="I19" s="7" t="inlineStr">
         <is>
-          <t>FB / Lemon8</t>
+          <t>IG / TikTok</t>
         </is>
       </c>
       <c r="J19" s="7" t="inlineStr">
         <is>
-          <t>Water purifier</t>
+          <t>Cordless vacuum</t>
         </is>
       </c>
       <c r="K19" s="7" t="inlineStr">
         <is>
-          <t>เครื่องกรองน้ำใช้ 20 นิ้ว</t>
+          <t>T12 Allergy Plus</t>
         </is>
       </c>
       <c r="L19" s="7" t="inlineStr">
         <is>
-          <t>น้ำดื่มกับน้ำใช้ ต้องกรองต่างกันยังไง</t>
+          <t>[ปลายฝน] พรม ที่นอน โซฟาที่อับชื้น: "ที่นอนก็ชื้นได้"</t>
         </is>
       </c>
       <c r="M19" s="8" t="n"/>
@@ -2218,19 +2234,19 @@
       </c>
       <c r="P19" s="7" t="inlineStr">
         <is>
-          <t>เตรียมเข้าฤดูฝุ่น PM2.5</t>
+          <t>23 ต.ค. วันหยุดยาว: content "วันหยุดจัดบ้านใหม่"</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>W5</t>
+          <t>W4</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>26 ต.ค.-1 พ.ย.</t>
+          <t>19-25 ต.ค.</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
@@ -2245,27 +2261,27 @@
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>Breathe + Drink</t>
+          <t>Body: บ้านควรช่วยให้ร่างกายพัก</t>
         </is>
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>ห้องนั่งเล่น / ห้องครัว</t>
+          <t>ห้องทำงาน / ห้องนอน</t>
         </is>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>E</t>
         </is>
       </c>
       <c r="H20" s="7" t="inlineStr">
         <is>
-          <t>Education / Explainer</t>
+          <t>LINE OA broadcast</t>
         </is>
       </c>
       <c r="I20" s="7" t="inlineStr">
         <is>
-          <t>FB / IG</t>
+          <t>LINE OA</t>
         </is>
       </c>
       <c r="J20" s="7" t="inlineStr">
@@ -2280,7 +2296,7 @@
       </c>
       <c r="L20" s="7" t="inlineStr">
         <is>
-          <t>สรุป Home Score เดือน ต.ค. (insight จาก quiz)</t>
+          <t>Mini sleep check ใน chat</t>
         </is>
       </c>
       <c r="M20" s="8" t="n"/>
@@ -2290,11 +2306,7 @@
           <t>Not started</t>
         </is>
       </c>
-      <c r="P20" s="7" t="inlineStr">
-        <is>
-          <t>เตรียมเข้าฤดูฝุ่น PM2.5</t>
-        </is>
-      </c>
+      <c r="P20" s="7" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
@@ -2329,32 +2341,32 @@
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H21" s="7" t="inlineStr">
         <is>
-          <t>LINE OA broadcast</t>
+          <t>Short video (hook 3 วิ)</t>
         </is>
       </c>
       <c r="I21" s="7" t="inlineStr">
         <is>
-          <t>LINE OA</t>
+          <t>TikTok / Reels</t>
         </is>
       </c>
       <c r="J21" s="7" t="inlineStr">
         <is>
-          <t>Cross-category</t>
+          <t>Air purifier</t>
         </is>
       </c>
       <c r="K21" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>AP-H3029US</t>
         </is>
       </c>
       <c r="L21" s="7" t="inlineStr">
         <is>
-          <t>Recap Home Score + ปูทาง 11.11 (ชวนเพิ่มเพื่อน)</t>
+          <t>"ปิดหน้าต่างแล้วฝุ่นในบ้านลดจริงไหม ลองวัดให้ดู" (ห้องนั่งเล่น 40–80 ตร.ม.)</t>
         </is>
       </c>
       <c r="M21" s="8" t="n"/>
@@ -2364,67 +2376,71 @@
           <t>Not started</t>
         </is>
       </c>
-      <c r="P21" s="7" t="inlineStr"/>
+      <c r="P21" s="7" t="inlineStr">
+        <is>
+          <t>เตรียมเข้าฤดูฝุ่น PM2.5</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="10" t="inlineStr">
-        <is>
-          <t>W6</t>
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>W5</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>2-8 พ.ย.</t>
+          <t>26 ต.ค.-1 พ.ย.</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>พ.ย. MOFU: ผลตรวจรายห้อง</t>
+          <t>ต.ค. TOFU: บ้านคุณป่วยอยู่หรือเปล่า</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>MOFU</t>
+          <t>TOFU</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>ผลตรวจห้องนอน</t>
+          <t>Breathe + Drink</t>
         </is>
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>ห้องนอน</t>
+          <t>ห้องนั่งเล่น / ห้องครัว</t>
         </is>
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H22" s="7" t="inlineStr">
         <is>
-          <t>Education / Explainer</t>
+          <t>Short video (hook 3 วิ)</t>
         </is>
       </c>
       <c r="I22" s="7" t="inlineStr">
         <is>
-          <t>FB / IG</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="J22" s="7" t="inlineStr">
         <is>
-          <t>Air purifier</t>
+          <t>Water purifier</t>
         </is>
       </c>
       <c r="K22" s="7" t="inlineStr">
         <is>
-          <t>CF-8428 / AP-8119US</t>
+          <t>RO แบบไร้ถัง / BW-D103</t>
         </is>
       </c>
       <c r="L22" s="7" t="inlineStr">
         <is>
-          <t>"ห้องไหนควรวางเครื่องฟอกก่อน" ห้องนอน 20–40 vs 10–30 ตร.ม.</t>
+          <t>"น้ำที่คุณดื่มที่บ้าน ผ่านอะไรมาบ้าง"</t>
         </is>
       </c>
       <c r="M22" s="8" t="n"/>
@@ -2436,69 +2452,69 @@
       </c>
       <c r="P22" s="7" t="inlineStr">
         <is>
-          <t>Brief KOL/UGC สำหรับ W7-W8</t>
+          <t>เตรียมเข้าฤดูฝุ่น PM2.5</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="10" t="inlineStr">
-        <is>
-          <t>W6</t>
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>W5</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>2-8 พ.ย.</t>
+          <t>26 ต.ค.-1 พ.ย.</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>พ.ย. MOFU: ผลตรวจรายห้อง</t>
+          <t>ต.ค. TOFU: บ้านคุณป่วยอยู่หรือเปล่า</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>MOFU</t>
+          <t>TOFU</t>
         </is>
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
-          <t>ผลตรวจห้องนอน</t>
+          <t>Breathe + Drink</t>
         </is>
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>ห้องนอน</t>
+          <t>ห้องนั่งเล่น / ห้องครัว</t>
         </is>
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H23" s="7" t="inlineStr">
         <is>
-          <t>Proof (UGC / testimonial / demo)</t>
+          <t>Education / Explainer</t>
         </is>
       </c>
       <c r="I23" s="7" t="inlineStr">
         <is>
-          <t>IG / TikTok</t>
+          <t>FB / Lemon8</t>
         </is>
       </c>
       <c r="J23" s="7" t="inlineStr">
         <is>
-          <t>Air purifier</t>
+          <t>Water purifier</t>
         </is>
       </c>
       <c r="K23" s="7" t="inlineStr">
         <is>
-          <t>CF-8428</t>
+          <t>เครื่องกรองน้ำใช้ 20 นิ้ว</t>
         </is>
       </c>
       <c r="L23" s="7" t="inlineStr">
         <is>
-          <t>Bedroom setup จริง</t>
+          <t>น้ำดื่มกับน้ำใช้ ต้องกรองต่างกันยังไง</t>
         </is>
       </c>
       <c r="M23" s="8" t="n"/>
@@ -2510,69 +2526,69 @@
       </c>
       <c r="P23" s="7" t="inlineStr">
         <is>
-          <t>Brief KOL/UGC สำหรับ W7-W8</t>
+          <t>เตรียมเข้าฤดูฝุ่น PM2.5</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="10" t="inlineStr">
-        <is>
-          <t>W6</t>
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>W5</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>2-8 พ.ย.</t>
+          <t>26 ต.ค.-1 พ.ย.</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>พ.ย. MOFU: ผลตรวจรายห้อง</t>
+          <t>ต.ค. TOFU: บ้านคุณป่วยอยู่หรือเปล่า</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>MOFU</t>
+          <t>TOFU</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>ผลตรวจห้องนอน</t>
+          <t>Breathe + Drink</t>
         </is>
       </c>
       <c r="F24" s="7" t="inlineStr">
         <is>
-          <t>ห้องนอน</t>
+          <t>ห้องนั่งเล่น / ห้องครัว</t>
         </is>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H24" s="7" t="inlineStr">
         <is>
-          <t>Proof (UGC / testimonial / demo)</t>
+          <t>Education / Explainer</t>
         </is>
       </c>
       <c r="I24" s="7" t="inlineStr">
         <is>
-          <t>FB</t>
+          <t>FB / IG</t>
         </is>
       </c>
       <c r="J24" s="7" t="inlineStr">
         <is>
-          <t>Health pillow</t>
+          <t>Cross-category</t>
         </is>
       </c>
       <c r="K24" s="7" t="inlineStr">
         <is>
-          <t>หมอนรองคอเพื่อสุขภาพ</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L24" s="7" t="inlineStr">
         <is>
-          <t>Review การนอนจากผู้ใช้จริง</t>
+          <t>สรุป Home Score เดือน ต.ค. (insight จาก quiz)</t>
         </is>
       </c>
       <c r="M24" s="8" t="n"/>
@@ -2584,69 +2600,69 @@
       </c>
       <c r="P24" s="7" t="inlineStr">
         <is>
-          <t>Brief KOL/UGC สำหรับ W7-W8</t>
+          <t>เตรียมเข้าฤดูฝุ่น PM2.5</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="10" t="inlineStr">
-        <is>
-          <t>W6</t>
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>W5</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>2-8 พ.ย.</t>
+          <t>26 ต.ค.-1 พ.ย.</t>
         </is>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
-          <t>พ.ย. MOFU: ผลตรวจรายห้อง</t>
+          <t>ต.ค. TOFU: บ้านคุณป่วยอยู่หรือเปล่า</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>MOFU</t>
+          <t>TOFU</t>
         </is>
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
-          <t>ผลตรวจห้องนอน</t>
+          <t>Breathe + Drink</t>
         </is>
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
-          <t>ห้องนอน</t>
+          <t>ห้องนั่งเล่น / ห้องครัว</t>
         </is>
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>S</t>
         </is>
       </c>
       <c r="H25" s="7" t="inlineStr">
         <is>
-          <t>Engagement (poll / quiz CTA / Q&amp;A)</t>
+          <t>Seasonal (ผูกฤดูกาล)</t>
         </is>
       </c>
       <c r="I25" s="7" t="inlineStr">
         <is>
-          <t>IG Stories</t>
+          <t>FB</t>
         </is>
       </c>
       <c r="J25" s="7" t="inlineStr">
         <is>
-          <t>Cross-category</t>
+          <t>Portable AC</t>
         </is>
       </c>
       <c r="K25" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>BPAC-09B / BPAC-12B</t>
         </is>
       </c>
       <c r="L25" s="7" t="inlineStr">
         <is>
-          <t>Q&amp;A ห้องนอน</t>
+          <t>[ปลายฝน] ห้องทำงานยังร้อนกลางวัน: "ฝนหยุด ความร้อนกลับมา"</t>
         </is>
       </c>
       <c r="M25" s="8" t="n"/>
@@ -2658,39 +2674,39 @@
       </c>
       <c r="P25" s="7" t="inlineStr">
         <is>
-          <t>Brief KOL/UGC สำหรับ W7-W8</t>
+          <t>เตรียมเข้าฤดูฝุ่น PM2.5</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="10" t="inlineStr">
-        <is>
-          <t>W6</t>
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>W5</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>2-8 พ.ย.</t>
+          <t>26 ต.ค.-1 พ.ย.</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>พ.ย. MOFU: ผลตรวจรายห้อง</t>
+          <t>ต.ค. TOFU: บ้านคุณป่วยอยู่หรือเปล่า</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>MOFU</t>
+          <t>TOFU</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>ผลตรวจห้องนอน</t>
+          <t>Breathe + Drink</t>
         </is>
       </c>
       <c r="F26" s="7" t="inlineStr">
         <is>
-          <t>ห้องนอน</t>
+          <t>ห้องนั่งเล่น / ห้องครัว</t>
         </is>
       </c>
       <c r="G26" s="7" t="inlineStr">
@@ -2720,7 +2736,7 @@
       </c>
       <c r="L26" s="7" t="inlineStr">
         <is>
-          <t>Segment broadcast ตาม tag quiz + early notify 11.11</t>
+          <t>Recap Home Score + ปูทาง 11.11 (ชวนเพิ่มเพื่อน)</t>
         </is>
       </c>
       <c r="M26" s="8" t="n"/>
@@ -2735,12 +2751,12 @@
     <row r="27">
       <c r="A27" s="10" t="inlineStr">
         <is>
-          <t>W7</t>
+          <t>W6</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>9-15 พ.ย.</t>
+          <t>2-8 พ.ย.</t>
         </is>
       </c>
       <c r="C27" s="7" t="inlineStr">
@@ -2755,42 +2771,42 @@
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>11.11: ห้องที่ใช้บ่อยที่สุด</t>
+          <t>ผลตรวจห้องนอน</t>
         </is>
       </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
-          <t>ห้องนั่งเล่น / ห้องครัว</t>
+          <t>ห้องนอน</t>
         </is>
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H27" s="7" t="inlineStr">
         <is>
-          <t>Short video (hook 3 วิ)</t>
+          <t>Education / Explainer</t>
         </is>
       </c>
       <c r="I27" s="7" t="inlineStr">
         <is>
-          <t>TikTok / Reels</t>
+          <t>FB / IG</t>
         </is>
       </c>
       <c r="J27" s="7" t="inlineStr">
         <is>
-          <t>Cross-category</t>
+          <t>Air purifier</t>
         </is>
       </c>
       <c r="K27" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>CF-8428 / AP-8119US</t>
         </is>
       </c>
       <c r="L27" s="7" t="inlineStr">
         <is>
-          <t>Countdown 11.11 "เลือกเครื่องตามผล Check-up"</t>
+          <t>"ห้องไหนควรวางเครื่องฟอกก่อน" ห้องนอน 20–40 vs 10–30 ตร.ม.</t>
         </is>
       </c>
       <c r="M27" s="8" t="n"/>
@@ -2802,19 +2818,19 @@
       </c>
       <c r="P27" s="7" t="inlineStr">
         <is>
-          <t>11.11 (พ.) ยิง social ไปลง marketplace</t>
+          <t>Brief KOL/UGC สำหรับ W7-W8</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="10" t="inlineStr">
         <is>
-          <t>W7</t>
+          <t>W6</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>9-15 พ.ย.</t>
+          <t>2-8 พ.ย.</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
@@ -2829,27 +2845,27 @@
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>11.11: ห้องที่ใช้บ่อยที่สุด</t>
+          <t>ผลตรวจห้องนอน</t>
         </is>
       </c>
       <c r="F28" s="7" t="inlineStr">
         <is>
-          <t>ห้องนั่งเล่น / ห้องครัว</t>
+          <t>ห้องนอน</t>
         </is>
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H28" s="7" t="inlineStr">
         <is>
-          <t>Education / Explainer</t>
+          <t>Proof (UGC / testimonial / demo)</t>
         </is>
       </c>
       <c r="I28" s="7" t="inlineStr">
         <is>
-          <t>FB / IG</t>
+          <t>IG / TikTok</t>
         </is>
       </c>
       <c r="J28" s="7" t="inlineStr">
@@ -2859,12 +2875,12 @@
       </c>
       <c r="K28" s="7" t="inlineStr">
         <is>
-          <t>AP-H3029US / CF-8428</t>
+          <t>CF-8428</t>
         </is>
       </c>
       <c r="L28" s="7" t="inlineStr">
         <is>
-          <t>ห้องนั่งเล่นใหญ่ vs เล็ก เลือกรุ่นตามพื้นที่</t>
+          <t>Bedroom setup จริง</t>
         </is>
       </c>
       <c r="M28" s="8" t="n"/>
@@ -2876,19 +2892,19 @@
       </c>
       <c r="P28" s="7" t="inlineStr">
         <is>
-          <t>11.11 (พ.) ยิง social ไปลง marketplace</t>
+          <t>Brief KOL/UGC สำหรับ W7-W8</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="10" t="inlineStr">
         <is>
-          <t>W7</t>
+          <t>W6</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>9-15 พ.ย.</t>
+          <t>2-8 พ.ย.</t>
         </is>
       </c>
       <c r="C29" s="7" t="inlineStr">
@@ -2903,12 +2919,12 @@
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
-          <t>11.11: ห้องที่ใช้บ่อยที่สุด</t>
+          <t>ผลตรวจห้องนอน</t>
         </is>
       </c>
       <c r="F29" s="7" t="inlineStr">
         <is>
-          <t>ห้องนั่งเล่น / ห้องครัว</t>
+          <t>ห้องนอน</t>
         </is>
       </c>
       <c r="G29" s="7" t="inlineStr">
@@ -2923,22 +2939,22 @@
       </c>
       <c r="I29" s="7" t="inlineStr">
         <is>
-          <t>FB / IG</t>
+          <t>FB</t>
         </is>
       </c>
       <c r="J29" s="7" t="inlineStr">
         <is>
-          <t>Water purifier</t>
+          <t>Health pillow</t>
         </is>
       </c>
       <c r="K29" s="7" t="inlineStr">
         <is>
-          <t>RO แบบไร้ถัง</t>
+          <t>หมอนรองคอเพื่อสุขภาพ</t>
         </is>
       </c>
       <c r="L29" s="7" t="inlineStr">
         <is>
-          <t>Testimonial ครัวที่บ้าน</t>
+          <t>Review การนอนจากผู้ใช้จริง</t>
         </is>
       </c>
       <c r="M29" s="8" t="n"/>
@@ -2950,19 +2966,19 @@
       </c>
       <c r="P29" s="7" t="inlineStr">
         <is>
-          <t>11.11 (พ.) ยิง social ไปลง marketplace</t>
+          <t>Brief KOL/UGC สำหรับ W7-W8</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="10" t="inlineStr">
         <is>
-          <t>W7</t>
+          <t>W6</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>9-15 พ.ย.</t>
+          <t>2-8 พ.ย.</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
@@ -2977,42 +2993,42 @@
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>11.11: ห้องที่ใช้บ่อยที่สุด</t>
+          <t>ผลตรวจห้องนอน</t>
         </is>
       </c>
       <c r="F30" s="7" t="inlineStr">
         <is>
-          <t>ห้องนั่งเล่น / ห้องครัว</t>
+          <t>ห้องนอน</t>
         </is>
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="H30" s="7" t="inlineStr">
         <is>
-          <t>Proof (UGC / testimonial / demo)</t>
+          <t>Engagement (poll / quiz CTA / Q&amp;A)</t>
         </is>
       </c>
       <c r="I30" s="7" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>IG Stories</t>
         </is>
       </c>
       <c r="J30" s="7" t="inlineStr">
         <is>
-          <t>Robot vacuum</t>
+          <t>Cross-category</t>
         </is>
       </c>
       <c r="K30" s="7" t="inlineStr">
         <is>
-          <t>L6C / L0 / Y1</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L30" s="7" t="inlineStr">
         <is>
-          <t>Day-in-life ครอบครัวทำงาน "กลับบ้านมาพื้นสะอาดแล้ว"</t>
+          <t>Q&amp;A ห้องนอน</t>
         </is>
       </c>
       <c r="M30" s="8" t="n"/>
@@ -3024,19 +3040,19 @@
       </c>
       <c r="P30" s="7" t="inlineStr">
         <is>
-          <t>11.11 (พ.) ยิง social ไปลง marketplace</t>
+          <t>Brief KOL/UGC สำหรับ W7-W8</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="10" t="inlineStr">
         <is>
-          <t>W7</t>
+          <t>W6</t>
         </is>
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>9-15 พ.ย.</t>
+          <t>2-8 พ.ย.</t>
         </is>
       </c>
       <c r="C31" s="7" t="inlineStr">
@@ -3051,42 +3067,42 @@
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
-          <t>11.11: ห้องที่ใช้บ่อยที่สุด</t>
+          <t>ผลตรวจห้องนอน</t>
         </is>
       </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
-          <t>ห้องนั่งเล่น / ห้องครัว</t>
+          <t>ห้องนอน</t>
         </is>
       </c>
       <c r="G31" s="7" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>S</t>
         </is>
       </c>
       <c r="H31" s="7" t="inlineStr">
         <is>
-          <t>LINE OA broadcast</t>
+          <t>Seasonal (ผูกฤดูกาล)</t>
         </is>
       </c>
       <c r="I31" s="7" t="inlineStr">
         <is>
-          <t>LINE OA</t>
+          <t>FB / IG</t>
         </is>
       </c>
       <c r="J31" s="7" t="inlineStr">
         <is>
-          <t>Cross-category</t>
+          <t>Air purifier</t>
         </is>
       </c>
       <c r="K31" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>CF-8428 / AP-8119US</t>
         </is>
       </c>
       <c r="L31" s="7" t="inlineStr">
         <is>
-          <t>Personalized prescription ตามผล quiz + offer [ ]</t>
+          <t>[ฝุ่น] วันไหนฝุ่นสูง เปิดหน้าต่างได้ไหม: "เช็คค่าฝุ่นก่อนเปิดหน้าต่าง"</t>
         </is>
       </c>
       <c r="M31" s="8" t="n"/>
@@ -3096,17 +3112,21 @@
           <t>Not started</t>
         </is>
       </c>
-      <c r="P31" s="7" t="inlineStr"/>
+      <c r="P31" s="7" t="inlineStr">
+        <is>
+          <t>Brief KOL/UGC สำหรับ W7-W8</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="10" t="inlineStr">
         <is>
-          <t>W8</t>
+          <t>W6</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>16-22 พ.ย.</t>
+          <t>2-8 พ.ย.</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
@@ -3121,42 +3141,42 @@
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>ผลตรวจห้องเด็ก</t>
+          <t>ผลตรวจห้องนอน</t>
         </is>
       </c>
       <c r="F32" s="7" t="inlineStr">
         <is>
-          <t>ห้องเด็ก</t>
+          <t>ห้องนอน</t>
         </is>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="H32" s="7" t="inlineStr">
         <is>
-          <t>Proof (UGC / testimonial / demo)</t>
+          <t>LINE OA broadcast</t>
         </is>
       </c>
       <c r="I32" s="7" t="inlineStr">
         <is>
-          <t>FB / IG</t>
+          <t>LINE OA</t>
         </is>
       </c>
       <c r="J32" s="7" t="inlineStr">
         <is>
-          <t>Air purifier</t>
+          <t>Cross-category</t>
         </is>
       </c>
       <c r="K32" s="7" t="inlineStr">
         <is>
-          <t>CF-8005 / AP-8119US</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L32" s="7" t="inlineStr">
         <is>
-          <t>"คืนแรกที่ลูกไม่ไอ" (UGC จริงเท่านั้น)</t>
+          <t>Segment broadcast ตาม tag quiz + early notify 11.11</t>
         </is>
       </c>
       <c r="M32" s="8" t="n"/>
@@ -3166,21 +3186,17 @@
           <t>Not started</t>
         </is>
       </c>
-      <c r="P32" s="7" t="inlineStr">
-        <is>
-          <t>Persona: Family Protector</t>
-        </is>
-      </c>
+      <c r="P32" s="7" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="10" t="inlineStr">
         <is>
-          <t>W8</t>
+          <t>W7</t>
         </is>
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>16-22 พ.ย.</t>
+          <t>9-15 พ.ย.</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
@@ -3195,42 +3211,42 @@
       </c>
       <c r="E33" s="7" t="inlineStr">
         <is>
-          <t>ผลตรวจห้องเด็ก</t>
+          <t>11.11: ห้องที่ใช้บ่อยที่สุด</t>
         </is>
       </c>
       <c r="F33" s="7" t="inlineStr">
         <is>
-          <t>ห้องเด็ก</t>
+          <t>ห้องนั่งเล่น / ห้องครัว</t>
         </is>
       </c>
       <c r="G33" s="7" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H33" s="7" t="inlineStr">
         <is>
-          <t>Education / Explainer</t>
+          <t>Short video (hook 3 วิ)</t>
         </is>
       </c>
       <c r="I33" s="7" t="inlineStr">
         <is>
-          <t>FB / Lemon8</t>
+          <t>TikTok / Reels</t>
         </is>
       </c>
       <c r="J33" s="7" t="inlineStr">
         <is>
-          <t>Water purifier</t>
+          <t>Cross-category</t>
         </is>
       </c>
       <c r="K33" s="7" t="inlineStr">
         <is>
-          <t>BW-D103 / AICSN-H3</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L33" s="7" t="inlineStr">
         <is>
-          <t>เลือกเครื่องกรองน้ำให้เหมาะกับบ้านและคอนโด ([spec จริง])</t>
+          <t>Countdown 11.11 "เลือกเครื่องตามผล Check-up"</t>
         </is>
       </c>
       <c r="M33" s="8" t="n"/>
@@ -3242,19 +3258,19 @@
       </c>
       <c r="P33" s="7" t="inlineStr">
         <is>
-          <t>Persona: Family Protector</t>
+          <t>11.11 (พ.) ยิง social ไปลง marketplace</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="10" t="inlineStr">
         <is>
-          <t>W8</t>
+          <t>W7</t>
         </is>
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>16-22 พ.ย.</t>
+          <t>9-15 พ.ย.</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
@@ -3269,42 +3285,42 @@
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
-          <t>ผลตรวจห้องเด็ก</t>
+          <t>11.11: ห้องที่ใช้บ่อยที่สุด</t>
         </is>
       </c>
       <c r="F34" s="7" t="inlineStr">
         <is>
-          <t>ห้องเด็ก</t>
+          <t>ห้องนั่งเล่น / ห้องครัว</t>
         </is>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H34" s="7" t="inlineStr">
         <is>
-          <t>Engagement (poll / quiz CTA / Q&amp;A)</t>
+          <t>Education / Explainer</t>
         </is>
       </c>
       <c r="I34" s="7" t="inlineStr">
         <is>
-          <t>FB Groups</t>
+          <t>FB / IG</t>
         </is>
       </c>
       <c r="J34" s="7" t="inlineStr">
         <is>
-          <t>Cross-category</t>
+          <t>Air purifier</t>
         </is>
       </c>
       <c r="K34" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>AP-H3029US / CF-8428</t>
         </is>
       </c>
       <c r="L34" s="7" t="inlineStr">
         <is>
-          <t>Q&amp;A กับพ่อแม่: ห้องลูกต้องเช็คอะไรบ้าง</t>
+          <t>ห้องนั่งเล่นใหญ่ vs เล็ก เลือกรุ่นตามพื้นที่</t>
         </is>
       </c>
       <c r="M34" s="8" t="n"/>
@@ -3316,19 +3332,19 @@
       </c>
       <c r="P34" s="7" t="inlineStr">
         <is>
-          <t>Persona: Family Protector</t>
+          <t>11.11 (พ.) ยิง social ไปลง marketplace</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>W8</t>
+          <t>W7</t>
         </is>
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>16-22 พ.ย.</t>
+          <t>9-15 พ.ย.</t>
         </is>
       </c>
       <c r="C35" s="7" t="inlineStr">
@@ -3343,42 +3359,42 @@
       </c>
       <c r="E35" s="7" t="inlineStr">
         <is>
-          <t>ผลตรวจห้องเด็ก</t>
+          <t>11.11: ห้องที่ใช้บ่อยที่สุด</t>
         </is>
       </c>
       <c r="F35" s="7" t="inlineStr">
         <is>
-          <t>ห้องเด็ก</t>
+          <t>ห้องนั่งเล่น / ห้องครัว</t>
         </is>
       </c>
       <c r="G35" s="7" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H35" s="7" t="inlineStr">
         <is>
-          <t>LINE OA broadcast</t>
+          <t>Proof (UGC / testimonial / demo)</t>
         </is>
       </c>
       <c r="I35" s="7" t="inlineStr">
         <is>
-          <t>LINE OA</t>
+          <t>FB / IG</t>
         </is>
       </c>
       <c r="J35" s="7" t="inlineStr">
         <is>
-          <t>Cross-category</t>
+          <t>Water purifier</t>
         </is>
       </c>
       <c r="K35" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>RO แบบไร้ถัง</t>
         </is>
       </c>
       <c r="L35" s="7" t="inlineStr">
         <is>
-          <t>เริ่ม PM2.5 Alert เมื่อค่าเกิน [threshold]</t>
+          <t>Testimonial ครัวที่บ้าน</t>
         </is>
       </c>
       <c r="M35" s="8" t="n"/>
@@ -3388,17 +3404,21 @@
           <t>Not started</t>
         </is>
       </c>
-      <c r="P35" s="7" t="inlineStr"/>
+      <c r="P35" s="7" t="inlineStr">
+        <is>
+          <t>11.11 (พ.) ยิง social ไปลง marketplace</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="10" t="inlineStr">
         <is>
-          <t>W9</t>
+          <t>W7</t>
         </is>
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>23-29 พ.ย.</t>
+          <t>9-15 พ.ย.</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
@@ -3413,42 +3433,42 @@
       </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
-          <t>ผลตรวจห้องทำงาน</t>
+          <t>11.11: ห้องที่ใช้บ่อยที่สุด</t>
         </is>
       </c>
       <c r="F36" s="7" t="inlineStr">
         <is>
-          <t>ห้องทำงาน / WFH</t>
+          <t>ห้องนั่งเล่น / ห้องครัว</t>
         </is>
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H36" s="7" t="inlineStr">
         <is>
-          <t>Short video (hook 3 วิ)</t>
+          <t>Proof (UGC / testimonial / demo)</t>
         </is>
       </c>
       <c r="I36" s="7" t="inlineStr">
         <is>
-          <t>TikTok / Reels</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="J36" s="7" t="inlineStr">
         <is>
-          <t>Ergonomic chair</t>
+          <t>Robot vacuum</t>
         </is>
       </c>
       <c r="K36" s="7" t="inlineStr">
         <is>
-          <t>Bjorn / Stella / Astrid / Agnes</t>
+          <t>L6C / L0 / Y1</t>
         </is>
       </c>
       <c r="L36" s="7" t="inlineStr">
         <is>
-          <t>Desk setup makeover</t>
+          <t>Day-in-life ครอบครัวทำงาน "กลับบ้านมาพื้นสะอาดแล้ว"</t>
         </is>
       </c>
       <c r="M36" s="8" t="n"/>
@@ -3460,19 +3480,19 @@
       </c>
       <c r="P36" s="7" t="inlineStr">
         <is>
-          <t>Loy Krathong [วันที่ TBC]: greeting เท่านั้น / Portable AC เป็น low season</t>
+          <t>11.11 (พ.) ยิง social ไปลง marketplace</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
         <is>
-          <t>W9</t>
+          <t>W7</t>
         </is>
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>23-29 พ.ย.</t>
+          <t>9-15 พ.ย.</t>
         </is>
       </c>
       <c r="C37" s="7" t="inlineStr">
@@ -3487,42 +3507,42 @@
       </c>
       <c r="E37" s="7" t="inlineStr">
         <is>
-          <t>ผลตรวจห้องทำงาน</t>
+          <t>11.11: ห้องที่ใช้บ่อยที่สุด</t>
         </is>
       </c>
       <c r="F37" s="7" t="inlineStr">
         <is>
-          <t>ห้องทำงาน / WFH</t>
+          <t>ห้องนั่งเล่น / ห้องครัว</t>
         </is>
       </c>
       <c r="G37" s="7" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="H37" s="7" t="inlineStr">
         <is>
-          <t>Education / Explainer</t>
+          <t>Seasonal (ผูกฤดูกาล)</t>
         </is>
       </c>
       <c r="I37" s="7" t="inlineStr">
         <is>
-          <t>FB</t>
+          <t>TikTok / Reels</t>
         </is>
       </c>
       <c r="J37" s="7" t="inlineStr">
         <is>
-          <t>Portable AC</t>
+          <t>Air purifier</t>
         </is>
       </c>
       <c r="K37" s="7" t="inlineStr">
         <is>
-          <t>BPAC-09B / BPAC-12B</t>
+          <t>AP-H3029US</t>
         </is>
       </c>
       <c r="L37" s="7" t="inlineStr">
         <is>
-          <t>"ห้องทำงานร้อนเฉพาะจุด ไม่ต้องติดแอร์ใหม่"</t>
+          <t>[ฝุ่น] ปิดบ้านหนีฝุ่นแล้วอากาศในห้องไม่ถ่ายเท: "ปิดบ้านหนีฝุ่น แล้วอากาศในห้องล่ะ"</t>
         </is>
       </c>
       <c r="M37" s="8" t="n"/>
@@ -3534,19 +3554,19 @@
       </c>
       <c r="P37" s="7" t="inlineStr">
         <is>
-          <t>Loy Krathong [วันที่ TBC]: greeting เท่านั้น / Portable AC เป็น low season</t>
+          <t>11.11 (พ.) ยิง social ไปลง marketplace</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="10" t="inlineStr">
         <is>
-          <t>W9</t>
+          <t>W7</t>
         </is>
       </c>
       <c r="B38" s="7" t="inlineStr">
         <is>
-          <t>23-29 พ.ย.</t>
+          <t>9-15 พ.ย.</t>
         </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
@@ -3561,42 +3581,42 @@
       </c>
       <c r="E38" s="7" t="inlineStr">
         <is>
-          <t>ผลตรวจห้องทำงาน</t>
+          <t>11.11: ห้องที่ใช้บ่อยที่สุด</t>
         </is>
       </c>
       <c r="F38" s="7" t="inlineStr">
         <is>
-          <t>ห้องทำงาน / WFH</t>
+          <t>ห้องนั่งเล่น / ห้องครัว</t>
         </is>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>E</t>
         </is>
       </c>
       <c r="H38" s="7" t="inlineStr">
         <is>
-          <t>Proof (UGC / testimonial / demo)</t>
+          <t>LINE OA broadcast</t>
         </is>
       </c>
       <c r="I38" s="7" t="inlineStr">
         <is>
-          <t>IG / TikTok</t>
+          <t>LINE OA</t>
         </is>
       </c>
       <c r="J38" s="7" t="inlineStr">
         <is>
-          <t>Cordless vacuum</t>
+          <t>Cross-category</t>
         </is>
       </c>
       <c r="K38" s="7" t="inlineStr">
         <is>
-          <t>201A / T12 Allergy Plus</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L38" s="7" t="inlineStr">
         <is>
-          <t>ดูดฝุ่นโต๊ะ คีย์บอร์ด โซฟา</t>
+          <t>Personalized prescription ตามผล quiz + offer [ ]</t>
         </is>
       </c>
       <c r="M38" s="8" t="n"/>
@@ -3606,21 +3626,17 @@
           <t>Not started</t>
         </is>
       </c>
-      <c r="P38" s="7" t="inlineStr">
-        <is>
-          <t>Loy Krathong [วันที่ TBC]: greeting เท่านั้น / Portable AC เป็น low season</t>
-        </is>
-      </c>
+      <c r="P38" s="7" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
         <is>
-          <t>W9</t>
+          <t>W8</t>
         </is>
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>23-29 พ.ย.</t>
+          <t>16-22 พ.ย.</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
@@ -3635,27 +3651,27 @@
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
-          <t>ผลตรวจห้องทำงาน</t>
+          <t>ผลตรวจห้องเด็ก</t>
         </is>
       </c>
       <c r="F39" s="7" t="inlineStr">
         <is>
-          <t>ห้องทำงาน / WFH</t>
+          <t>ห้องเด็ก</t>
         </is>
       </c>
       <c r="G39" s="7" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H39" s="7" t="inlineStr">
         <is>
-          <t>Education / Explainer</t>
+          <t>Proof (UGC / testimonial / demo)</t>
         </is>
       </c>
       <c r="I39" s="7" t="inlineStr">
         <is>
-          <t>IG</t>
+          <t>FB / IG</t>
         </is>
       </c>
       <c r="J39" s="7" t="inlineStr">
@@ -3665,12 +3681,12 @@
       </c>
       <c r="K39" s="7" t="inlineStr">
         <is>
-          <t>CF-8005</t>
+          <t>CF-8005 / AP-8119US</t>
         </is>
       </c>
       <c r="L39" s="7" t="inlineStr">
         <is>
-          <t>เครื่องฟอกข้างโต๊ะทำงาน 10–20 ตร.ม.</t>
+          <t>"คืนแรกที่ลูกไม่ไอ" (UGC จริงเท่านั้น)</t>
         </is>
       </c>
       <c r="M39" s="8" t="n"/>
@@ -3682,19 +3698,19 @@
       </c>
       <c r="P39" s="7" t="inlineStr">
         <is>
-          <t>Loy Krathong [วันที่ TBC]: greeting เท่านั้น / Portable AC เป็น low season</t>
+          <t>Persona: Family Protector</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="10" t="inlineStr">
         <is>
-          <t>W9</t>
+          <t>W8</t>
         </is>
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>23-29 พ.ย.</t>
+          <t>16-22 พ.ย.</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
@@ -3709,42 +3725,42 @@
       </c>
       <c r="E40" s="7" t="inlineStr">
         <is>
-          <t>ผลตรวจห้องทำงาน</t>
+          <t>ผลตรวจห้องเด็ก</t>
         </is>
       </c>
       <c r="F40" s="7" t="inlineStr">
         <is>
-          <t>ห้องทำงาน / WFH</t>
+          <t>ห้องเด็ก</t>
         </is>
       </c>
       <c r="G40" s="7" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H40" s="7" t="inlineStr">
         <is>
-          <t>LINE OA broadcast</t>
+          <t>Education / Explainer</t>
         </is>
       </c>
       <c r="I40" s="7" t="inlineStr">
         <is>
-          <t>LINE OA</t>
+          <t>FB / Lemon8</t>
         </is>
       </c>
       <c r="J40" s="7" t="inlineStr">
         <is>
-          <t>Cross-category</t>
+          <t>Water purifier</t>
         </is>
       </c>
       <c r="K40" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>BW-D103 / AICSN-H3</t>
         </is>
       </c>
       <c r="L40" s="7" t="inlineStr">
         <is>
-          <t>Owner Care Series สำหรับคนซื้อช่วง 11.11 + filter info</t>
+          <t>เลือกเครื่องกรองน้ำให้เหมาะกับบ้านและคอนโด ([spec จริง])</t>
         </is>
       </c>
       <c r="M40" s="8" t="n"/>
@@ -3754,17 +3770,21 @@
           <t>Not started</t>
         </is>
       </c>
-      <c r="P40" s="7" t="inlineStr"/>
+      <c r="P40" s="7" t="inlineStr">
+        <is>
+          <t>Persona: Family Protector</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="10" t="inlineStr">
         <is>
-          <t>W10</t>
+          <t>W8</t>
         </is>
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>30 พ.ย.-6 ธ.ค.</t>
+          <t>16-22 พ.ย.</t>
         </is>
       </c>
       <c r="C41" s="7" t="inlineStr">
@@ -3779,42 +3799,42 @@
       </c>
       <c r="E41" s="7" t="inlineStr">
         <is>
-          <t>ของขวัญดูแลพ่อ</t>
+          <t>ผลตรวจห้องเด็ก</t>
         </is>
       </c>
       <c r="F41" s="7" t="inlineStr">
         <is>
-          <t>ห้องทำงาน / รถยนต์</t>
+          <t>ห้องเด็ก</t>
         </is>
       </c>
       <c r="G41" s="7" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="H41" s="7" t="inlineStr">
         <is>
-          <t>Education / Explainer</t>
+          <t>Engagement (poll / quiz CTA / Q&amp;A)</t>
         </is>
       </c>
       <c r="I41" s="7" t="inlineStr">
         <is>
-          <t>FB / IG</t>
+          <t>FB Groups</t>
         </is>
       </c>
       <c r="J41" s="7" t="inlineStr">
         <is>
-          <t>Ergonomic chair</t>
+          <t>Cross-category</t>
         </is>
       </c>
       <c r="K41" s="7" t="inlineStr">
         <is>
-          <t>Bjorn / Stella / Astrid / Agnes + ที่วางเท้าเพื่อสุขภาพ</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L41" s="7" t="inlineStr">
         <is>
-          <t>Gift guide "ดูแลสุขภาพพ่อ"</t>
+          <t>Q&amp;A กับพ่อแม่: ห้องลูกต้องเช็คอะไรบ้าง</t>
         </is>
       </c>
       <c r="M41" s="8" t="n"/>
@@ -3826,19 +3846,19 @@
       </c>
       <c r="P41" s="7" t="inlineStr">
         <is>
-          <t>5 ธ.ค. วันพ่อ: tone อบอุ่น ไม่ hard sell</t>
+          <t>Persona: Family Protector</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="10" t="inlineStr">
         <is>
-          <t>W10</t>
+          <t>W8</t>
         </is>
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>30 พ.ย.-6 ธ.ค.</t>
+          <t>16-22 พ.ย.</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
@@ -3853,42 +3873,42 @@
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t>ของขวัญดูแลพ่อ</t>
+          <t>ผลตรวจห้องเด็ก</t>
         </is>
       </c>
       <c r="F42" s="7" t="inlineStr">
         <is>
-          <t>ห้องทำงาน / รถยนต์</t>
+          <t>ห้องเด็ก</t>
         </is>
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>S</t>
         </is>
       </c>
       <c r="H42" s="7" t="inlineStr">
         <is>
-          <t>Proof (UGC / testimonial / demo)</t>
+          <t>Seasonal (ผูกฤดูกาล)</t>
         </is>
       </c>
       <c r="I42" s="7" t="inlineStr">
         <is>
-          <t>FB / IG</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="J42" s="7" t="inlineStr">
         <is>
-          <t>Health pillow</t>
+          <t>Air purifier</t>
         </is>
       </c>
       <c r="K42" s="7" t="inlineStr">
         <is>
-          <t>เบาะรองหลัง / หมอนรองคอสำหรับรถยนต์</t>
+          <t>เครื่องฟอกอากาศในรถยนต์</t>
         </is>
       </c>
       <c r="L42" s="7" t="inlineStr">
         <is>
-          <t>Story "พ่อขับรถทุกวัน"</t>
+          <t>[ฝุ่น] รถติดวันฝุ่นสูง: "รถติดวันฝุ่นเยอะ อากาศในรถเป็นยังไง"</t>
         </is>
       </c>
       <c r="M42" s="8" t="n"/>
@@ -3900,19 +3920,19 @@
       </c>
       <c r="P42" s="7" t="inlineStr">
         <is>
-          <t>5 ธ.ค. วันพ่อ: tone อบอุ่น ไม่ hard sell</t>
+          <t>Persona: Family Protector</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="10" t="inlineStr">
         <is>
-          <t>W10</t>
+          <t>W8</t>
         </is>
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>30 พ.ย.-6 ธ.ค.</t>
+          <t>16-22 พ.ย.</t>
         </is>
       </c>
       <c r="C43" s="7" t="inlineStr">
@@ -3927,42 +3947,42 @@
       </c>
       <c r="E43" s="7" t="inlineStr">
         <is>
-          <t>ของขวัญดูแลพ่อ</t>
+          <t>ผลตรวจห้องเด็ก</t>
         </is>
       </c>
       <c r="F43" s="7" t="inlineStr">
         <is>
-          <t>ห้องทำงาน / รถยนต์</t>
+          <t>ห้องเด็ก</t>
         </is>
       </c>
       <c r="G43" s="7" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>S</t>
         </is>
       </c>
       <c r="H43" s="7" t="inlineStr">
         <is>
-          <t>Short video (hook 3 วิ)</t>
+          <t>Seasonal (ผูกฤดูกาล)</t>
         </is>
       </c>
       <c r="I43" s="7" t="inlineStr">
         <is>
-          <t>TikTok</t>
+          <t>FB</t>
         </is>
       </c>
       <c r="J43" s="7" t="inlineStr">
         <is>
-          <t>Air purifier</t>
+          <t>Water purifier</t>
         </is>
       </c>
       <c r="K43" s="7" t="inlineStr">
         <is>
-          <t>เครื่องฟอกอากาศในรถยนต์</t>
+          <t>RO แบบไร้ถัง / BW-D103</t>
         </is>
       </c>
       <c r="L43" s="7" t="inlineStr">
         <is>
-          <t>อากาศในรถที่พ่อนั่งทุกวัน</t>
+          <t>[ฝุ่น] อยู่บ้านมากขึ้น ใช้น้ำดื่มมากขึ้น: "หลบฝุ่นอยู่บ้าน น้ำดื่มพอไหม"</t>
         </is>
       </c>
       <c r="M43" s="8" t="n"/>
@@ -3974,19 +3994,19 @@
       </c>
       <c r="P43" s="7" t="inlineStr">
         <is>
-          <t>5 ธ.ค. วันพ่อ: tone อบอุ่น ไม่ hard sell</t>
+          <t>Persona: Family Protector</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
         <is>
-          <t>W10</t>
+          <t>W8</t>
         </is>
       </c>
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>30 พ.ย.-6 ธ.ค.</t>
+          <t>16-22 พ.ย.</t>
         </is>
       </c>
       <c r="C44" s="7" t="inlineStr">
@@ -4001,27 +4021,27 @@
       </c>
       <c r="E44" s="7" t="inlineStr">
         <is>
-          <t>ของขวัญดูแลพ่อ</t>
+          <t>ผลตรวจห้องเด็ก</t>
         </is>
       </c>
       <c r="F44" s="7" t="inlineStr">
         <is>
-          <t>ห้องทำงาน / รถยนต์</t>
+          <t>ห้องเด็ก</t>
         </is>
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>E</t>
         </is>
       </c>
       <c r="H44" s="7" t="inlineStr">
         <is>
-          <t>Engagement (poll / quiz CTA / Q&amp;A)</t>
+          <t>LINE OA broadcast</t>
         </is>
       </c>
       <c r="I44" s="7" t="inlineStr">
         <is>
-          <t>FB</t>
+          <t>LINE OA</t>
         </is>
       </c>
       <c r="J44" s="7" t="inlineStr">
@@ -4036,7 +4056,7 @@
       </c>
       <c r="L44" s="7" t="inlineStr">
         <is>
-          <t>"พ่อคุณปวดหลังไหม" poll</t>
+          <t>เริ่ม PM2.5 Alert เมื่อค่าเกิน [threshold]</t>
         </is>
       </c>
       <c r="M44" s="8" t="n"/>
@@ -4046,21 +4066,17 @@
           <t>Not started</t>
         </is>
       </c>
-      <c r="P44" s="7" t="inlineStr">
-        <is>
-          <t>5 ธ.ค. วันพ่อ: tone อบอุ่น ไม่ hard sell</t>
-        </is>
-      </c>
+      <c r="P44" s="7" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="10" t="inlineStr">
         <is>
-          <t>W10</t>
+          <t>W9</t>
         </is>
       </c>
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>30 พ.ย.-6 ธ.ค.</t>
+          <t>23-29 พ.ย.</t>
         </is>
       </c>
       <c r="C45" s="7" t="inlineStr">
@@ -4075,42 +4091,42 @@
       </c>
       <c r="E45" s="7" t="inlineStr">
         <is>
-          <t>ของขวัญดูแลพ่อ</t>
+          <t>ผลตรวจห้องทำงาน</t>
         </is>
       </c>
       <c r="F45" s="7" t="inlineStr">
         <is>
-          <t>ห้องทำงาน / รถยนต์</t>
+          <t>ห้องทำงาน / WFH</t>
         </is>
       </c>
       <c r="G45" s="7" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H45" s="7" t="inlineStr">
         <is>
-          <t>LINE OA broadcast</t>
+          <t>Short video (hook 3 วิ)</t>
         </is>
       </c>
       <c r="I45" s="7" t="inlineStr">
         <is>
-          <t>LINE OA</t>
+          <t>TikTok / Reels</t>
         </is>
       </c>
       <c r="J45" s="7" t="inlineStr">
         <is>
-          <t>Cross-category</t>
+          <t>Ergonomic chair</t>
         </is>
       </c>
       <c r="K45" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Bjorn / Stella / Astrid / Agnes</t>
         </is>
       </c>
       <c r="L45" s="7" t="inlineStr">
         <is>
-          <t>Father's Day gift guide</t>
+          <t>Desk setup makeover</t>
         </is>
       </c>
       <c r="M45" s="8" t="n"/>
@@ -4120,37 +4136,41 @@
           <t>Not started</t>
         </is>
       </c>
-      <c r="P45" s="7" t="inlineStr"/>
+      <c r="P45" s="7" t="inlineStr">
+        <is>
+          <t>Loy Krathong [วันที่ TBC]: greeting เท่านั้น / Portable AC เป็น low season</t>
+        </is>
+      </c>
     </row>
     <row r="46">
-      <c r="A46" s="11" t="inlineStr">
-        <is>
-          <t>W11</t>
+      <c r="A46" s="10" t="inlineStr">
+        <is>
+          <t>W9</t>
         </is>
       </c>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>7-13 ธ.ค.</t>
+          <t>23-29 พ.ย.</t>
         </is>
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>ธ.ค. BOFU: ใบสั่งยาสำหรับบ้าน (Home Prescription)</t>
+          <t>พ.ย. MOFU: ผลตรวจรายห้อง</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>BOFU</t>
+          <t>MOFU</t>
         </is>
       </c>
       <c r="E46" s="7" t="inlineStr">
         <is>
-          <t>12.12 Home Prescription</t>
+          <t>ผลตรวจห้องทำงาน</t>
         </is>
       </c>
       <c r="F46" s="7" t="inlineStr">
         <is>
-          <t>ทั้งบ้าน</t>
+          <t>ห้องทำงาน / WFH</t>
         </is>
       </c>
       <c r="G46" s="7" t="inlineStr">
@@ -4165,22 +4185,22 @@
       </c>
       <c r="I46" s="7" t="inlineStr">
         <is>
-          <t>FB / IG</t>
+          <t>FB</t>
         </is>
       </c>
       <c r="J46" s="7" t="inlineStr">
         <is>
-          <t>Cross-category</t>
+          <t>Portable AC</t>
         </is>
       </c>
       <c r="K46" s="7" t="inlineStr">
         <is>
-          <t>Bedroom: AP-8119US + หมอนรองคอ</t>
+          <t>BPAC-09B / BPAC-12B</t>
         </is>
       </c>
       <c r="L46" s="7" t="inlineStr">
         <is>
-          <t>"ใบสั่งยาห้องนอน" (bundle proposal)</t>
+          <t>"ห้องทำงานร้อนเฉพาะจุด ไม่ต้องติดแอร์ใหม่"</t>
         </is>
       </c>
       <c r="M46" s="8" t="n"/>
@@ -4192,69 +4212,69 @@
       </c>
       <c r="P46" s="7" t="inlineStr">
         <is>
-          <t>12.12 (ส.), 10 ธ.ค. วันหยุด / bundle เป็น proposal รอ confirm offer</t>
+          <t>Loy Krathong [วันที่ TBC]: greeting เท่านั้น / Portable AC เป็น low season</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="11" t="inlineStr">
-        <is>
-          <t>W11</t>
+      <c r="A47" s="10" t="inlineStr">
+        <is>
+          <t>W9</t>
         </is>
       </c>
       <c r="B47" s="7" t="inlineStr">
         <is>
-          <t>7-13 ธ.ค.</t>
+          <t>23-29 พ.ย.</t>
         </is>
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
-          <t>ธ.ค. BOFU: ใบสั่งยาสำหรับบ้าน (Home Prescription)</t>
+          <t>พ.ย. MOFU: ผลตรวจรายห้อง</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>BOFU</t>
+          <t>MOFU</t>
         </is>
       </c>
       <c r="E47" s="7" t="inlineStr">
         <is>
-          <t>12.12 Home Prescription</t>
+          <t>ผลตรวจห้องทำงาน</t>
         </is>
       </c>
       <c r="F47" s="7" t="inlineStr">
         <is>
-          <t>ทั้งบ้าน</t>
+          <t>ห้องทำงาน / WFH</t>
         </is>
       </c>
       <c r="G47" s="7" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H47" s="7" t="inlineStr">
         <is>
-          <t>Education / Explainer</t>
+          <t>Proof (UGC / testimonial / demo)</t>
         </is>
       </c>
       <c r="I47" s="7" t="inlineStr">
         <is>
-          <t>FB / IG</t>
+          <t>IG / TikTok</t>
         </is>
       </c>
       <c r="J47" s="7" t="inlineStr">
         <is>
-          <t>Cross-category</t>
+          <t>Cordless vacuum</t>
         </is>
       </c>
       <c r="K47" s="7" t="inlineStr">
         <is>
-          <t>Family: CF-8428 + RO แบบไร้ถัง</t>
+          <t>201A / T12 Allergy Plus</t>
         </is>
       </c>
       <c r="L47" s="7" t="inlineStr">
         <is>
-          <t>"ใบสั่งยาบ้านมีเด็ก" (bundle proposal)</t>
+          <t>ดูดฝุ่นโต๊ะ คีย์บอร์ด โซฟา</t>
         </is>
       </c>
       <c r="M47" s="8" t="n"/>
@@ -4266,69 +4286,69 @@
       </c>
       <c r="P47" s="7" t="inlineStr">
         <is>
-          <t>12.12 (ส.), 10 ธ.ค. วันหยุด / bundle เป็น proposal รอ confirm offer</t>
+          <t>Loy Krathong [วันที่ TBC]: greeting เท่านั้น / Portable AC เป็น low season</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="11" t="inlineStr">
-        <is>
-          <t>W11</t>
+      <c r="A48" s="10" t="inlineStr">
+        <is>
+          <t>W9</t>
         </is>
       </c>
       <c r="B48" s="7" t="inlineStr">
         <is>
-          <t>7-13 ธ.ค.</t>
+          <t>23-29 พ.ย.</t>
         </is>
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>ธ.ค. BOFU: ใบสั่งยาสำหรับบ้าน (Home Prescription)</t>
+          <t>พ.ย. MOFU: ผลตรวจรายห้อง</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>BOFU</t>
+          <t>MOFU</t>
         </is>
       </c>
       <c r="E48" s="7" t="inlineStr">
         <is>
-          <t>12.12 Home Prescription</t>
+          <t>ผลตรวจห้องทำงาน</t>
         </is>
       </c>
       <c r="F48" s="7" t="inlineStr">
         <is>
-          <t>ทั้งบ้าน</t>
+          <t>ห้องทำงาน / WFH</t>
         </is>
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H48" s="7" t="inlineStr">
         <is>
-          <t>Short video (hook 3 วิ)</t>
+          <t>Education / Explainer</t>
         </is>
       </c>
       <c r="I48" s="7" t="inlineStr">
         <is>
-          <t>TikTok / Reels</t>
+          <t>IG</t>
         </is>
       </c>
       <c r="J48" s="7" t="inlineStr">
         <is>
-          <t>Cross-category</t>
+          <t>Air purifier</t>
         </is>
       </c>
       <c r="K48" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>CF-8005</t>
         </is>
       </c>
       <c r="L48" s="7" t="inlineStr">
         <is>
-          <t>12.12 countdown</t>
+          <t>เครื่องฟอกข้างโต๊ะทำงาน 10–20 ตร.ม.</t>
         </is>
       </c>
       <c r="M48" s="8" t="n"/>
@@ -4340,69 +4360,69 @@
       </c>
       <c r="P48" s="7" t="inlineStr">
         <is>
-          <t>12.12 (ส.), 10 ธ.ค. วันหยุด / bundle เป็น proposal รอ confirm offer</t>
+          <t>Loy Krathong [วันที่ TBC]: greeting เท่านั้น / Portable AC เป็น low season</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="11" t="inlineStr">
-        <is>
-          <t>W11</t>
+      <c r="A49" s="10" t="inlineStr">
+        <is>
+          <t>W9</t>
         </is>
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>7-13 ธ.ค.</t>
+          <t>23-29 พ.ย.</t>
         </is>
       </c>
       <c r="C49" s="7" t="inlineStr">
         <is>
-          <t>ธ.ค. BOFU: ใบสั่งยาสำหรับบ้าน (Home Prescription)</t>
+          <t>พ.ย. MOFU: ผลตรวจรายห้อง</t>
         </is>
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>BOFU</t>
+          <t>MOFU</t>
         </is>
       </c>
       <c r="E49" s="7" t="inlineStr">
         <is>
-          <t>12.12 Home Prescription</t>
+          <t>ผลตรวจห้องทำงาน</t>
         </is>
       </c>
       <c r="F49" s="7" t="inlineStr">
         <is>
-          <t>ทั้งบ้าน</t>
+          <t>ห้องทำงาน / WFH</t>
         </is>
       </c>
       <c r="G49" s="7" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>S</t>
         </is>
       </c>
       <c r="H49" s="7" t="inlineStr">
         <is>
-          <t>Proof (UGC / testimonial / demo)</t>
+          <t>Seasonal (ผูกฤดูกาล)</t>
         </is>
       </c>
       <c r="I49" s="7" t="inlineStr">
         <is>
-          <t>Meta retargeting</t>
+          <t>FB / LINE</t>
         </is>
       </c>
       <c r="J49" s="7" t="inlineStr">
         <is>
-          <t>Cross-category</t>
+          <t>Air purifier</t>
         </is>
       </c>
       <c r="K49" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>แผ่นฟอกตรงรุ่น</t>
         </is>
       </c>
       <c r="L49" s="7" t="inlineStr">
         <is>
-          <t>Retarget คนที่ทำ quiz แล้ว ตามผล Home Score</t>
+          <t>[ฝุ่น] เตือนเช็คแผ่นฟอกก่อนฝุ่นหนัก: "เครื่องฟอกทำงานหนัก แผ่นฟอกพร้อมหรือยัง"</t>
         </is>
       </c>
       <c r="M49" s="8" t="n"/>
@@ -4414,69 +4434,69 @@
       </c>
       <c r="P49" s="7" t="inlineStr">
         <is>
-          <t>12.12 (ส.), 10 ธ.ค. วันหยุด / bundle เป็น proposal รอ confirm offer</t>
+          <t>Loy Krathong [วันที่ TBC]: greeting เท่านั้น / Portable AC เป็น low season</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="11" t="inlineStr">
-        <is>
-          <t>W11</t>
+      <c r="A50" s="10" t="inlineStr">
+        <is>
+          <t>W9</t>
         </is>
       </c>
       <c r="B50" s="7" t="inlineStr">
         <is>
-          <t>7-13 ธ.ค.</t>
+          <t>23-29 พ.ย.</t>
         </is>
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
-          <t>ธ.ค. BOFU: ใบสั่งยาสำหรับบ้าน (Home Prescription)</t>
+          <t>พ.ย. MOFU: ผลตรวจรายห้อง</t>
         </is>
       </c>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>BOFU</t>
+          <t>MOFU</t>
         </is>
       </c>
       <c r="E50" s="7" t="inlineStr">
         <is>
-          <t>12.12 Home Prescription</t>
+          <t>ผลตรวจห้องทำงาน</t>
         </is>
       </c>
       <c r="F50" s="7" t="inlineStr">
         <is>
-          <t>ทั้งบ้าน</t>
+          <t>ห้องทำงาน / WFH</t>
         </is>
       </c>
       <c r="G50" s="7" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>S</t>
         </is>
       </c>
       <c r="H50" s="7" t="inlineStr">
         <is>
-          <t>LINE OA broadcast</t>
+          <t>Seasonal (ผูกฤดูกาล)</t>
         </is>
       </c>
       <c r="I50" s="7" t="inlineStr">
         <is>
-          <t>LINE OA</t>
+          <t>IG / Lemon8</t>
         </is>
       </c>
       <c r="J50" s="7" t="inlineStr">
         <is>
-          <t>Cross-category</t>
+          <t>Ergonomic chair</t>
         </is>
       </c>
       <c r="K50" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Bjorn / Stella / Astrid / Agnes</t>
         </is>
       </c>
       <c r="L50" s="7" t="inlineStr">
         <is>
-          <t>Prescription bundle ตาม tag + 12.12 offer [ ]</t>
+          <t>[ฝุ่น] WFH ช่วงฝุ่นสูง: "ฝุ่นเยอะ ทำงานที่บ้าน หลังรับไหวไหม"</t>
         </is>
       </c>
       <c r="M50" s="8" t="n"/>
@@ -4486,67 +4506,71 @@
           <t>Not started</t>
         </is>
       </c>
-      <c r="P50" s="7" t="inlineStr"/>
+      <c r="P50" s="7" t="inlineStr">
+        <is>
+          <t>Loy Krathong [วันที่ TBC]: greeting เท่านั้น / Portable AC เป็น low season</t>
+        </is>
+      </c>
     </row>
     <row r="51">
-      <c r="A51" s="11" t="inlineStr">
-        <is>
-          <t>W12</t>
+      <c r="A51" s="10" t="inlineStr">
+        <is>
+          <t>W9</t>
         </is>
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>14-20 ธ.ค.</t>
+          <t>23-29 พ.ย.</t>
         </is>
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
-          <t>ธ.ค. BOFU: ใบสั่งยาสำหรับบ้าน (Home Prescription)</t>
+          <t>พ.ย. MOFU: ผลตรวจรายห้อง</t>
         </is>
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>BOFU</t>
+          <t>MOFU</t>
         </is>
       </c>
       <c r="E51" s="7" t="inlineStr">
         <is>
-          <t>Gift of Wellness + ห้องน้ำหน้าหนาว</t>
+          <t>ผลตรวจห้องทำงาน</t>
         </is>
       </c>
       <c r="F51" s="7" t="inlineStr">
         <is>
-          <t>ห้องน้ำ / Self-care</t>
+          <t>ห้องทำงาน / WFH</t>
         </is>
       </c>
       <c r="G51" s="7" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>E</t>
         </is>
       </c>
       <c r="H51" s="7" t="inlineStr">
         <is>
-          <t>Short video (hook 3 วิ)</t>
+          <t>LINE OA broadcast</t>
         </is>
       </c>
       <c r="I51" s="7" t="inlineStr">
         <is>
-          <t>TikTok / IG</t>
+          <t>LINE OA</t>
         </is>
       </c>
       <c r="J51" s="7" t="inlineStr">
         <is>
-          <t>Hair styling</t>
+          <t>Cross-category</t>
         </is>
       </c>
       <c r="K51" s="7" t="inlineStr">
         <is>
-          <t>BSL-01 / BSL-02</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L51" s="7" t="inlineStr">
         <is>
-          <t>GRWM "ช่วงปาร์ตี้ จัดทรงทุกวันแต่ผมไม่เสีย"</t>
+          <t>Owner Care Series สำหรับคนซื้อช่วง 11.11 + filter info</t>
         </is>
       </c>
       <c r="M51" s="8" t="n"/>
@@ -4556,41 +4580,37 @@
           <t>Not started</t>
         </is>
       </c>
-      <c r="P51" s="7" t="inlineStr">
-        <is>
-          <t>Beauty sub-brand ใช้ logo Beauty / ELCB: ยืนยันรุ่นที่มีก่อนโพส</t>
-        </is>
-      </c>
+      <c r="P51" s="7" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="11" t="inlineStr">
-        <is>
-          <t>W12</t>
+      <c r="A52" s="10" t="inlineStr">
+        <is>
+          <t>W10</t>
         </is>
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>14-20 ธ.ค.</t>
+          <t>30 พ.ย.-6 ธ.ค.</t>
         </is>
       </c>
       <c r="C52" s="7" t="inlineStr">
         <is>
-          <t>ธ.ค. BOFU: ใบสั่งยาสำหรับบ้าน (Home Prescription)</t>
+          <t>พ.ย. MOFU: ผลตรวจรายห้อง</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>BOFU</t>
+          <t>MOFU</t>
         </is>
       </c>
       <c r="E52" s="7" t="inlineStr">
         <is>
-          <t>Gift of Wellness + ห้องน้ำหน้าหนาว</t>
+          <t>ของขวัญดูแลพ่อ</t>
         </is>
       </c>
       <c r="F52" s="7" t="inlineStr">
         <is>
-          <t>ห้องน้ำ / Self-care</t>
+          <t>ห้องทำงาน / รถยนต์</t>
         </is>
       </c>
       <c r="G52" s="7" t="inlineStr">
@@ -4610,17 +4630,17 @@
       </c>
       <c r="J52" s="7" t="inlineStr">
         <is>
-          <t>Water heater</t>
+          <t>Ergonomic chair</t>
         </is>
       </c>
       <c r="K52" s="7" t="inlineStr">
         <is>
-          <t>FELIX / LUKA / ELKA / Konrad</t>
+          <t>Bjorn / Stella / Astrid / Agnes + ที่วางเท้าเพื่อสุขภาพ</t>
         </is>
       </c>
       <c r="L52" s="7" t="inlineStr">
         <is>
-          <t>"ลมหนาวมาแล้ว ห้องน้ำบ้านคุณปลอดภัยไหม" (ระบบตัดไฟ ELCB)</t>
+          <t>Gift guide "ดูแลสุขภาพพ่อ"</t>
         </is>
       </c>
       <c r="M52" s="8" t="n"/>
@@ -4632,69 +4652,69 @@
       </c>
       <c r="P52" s="7" t="inlineStr">
         <is>
-          <t>Beauty sub-brand ใช้ logo Beauty / ELCB: ยืนยันรุ่นที่มีก่อนโพส</t>
+          <t>5 ธ.ค. วันพ่อ: tone อบอุ่น ไม่ hard sell</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="11" t="inlineStr">
-        <is>
-          <t>W12</t>
+      <c r="A53" s="10" t="inlineStr">
+        <is>
+          <t>W10</t>
         </is>
       </c>
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>14-20 ธ.ค.</t>
+          <t>30 พ.ย.-6 ธ.ค.</t>
         </is>
       </c>
       <c r="C53" s="7" t="inlineStr">
         <is>
-          <t>ธ.ค. BOFU: ใบสั่งยาสำหรับบ้าน (Home Prescription)</t>
+          <t>พ.ย. MOFU: ผลตรวจรายห้อง</t>
         </is>
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>BOFU</t>
+          <t>MOFU</t>
         </is>
       </c>
       <c r="E53" s="7" t="inlineStr">
         <is>
-          <t>Gift of Wellness + ห้องน้ำหน้าหนาว</t>
+          <t>ของขวัญดูแลพ่อ</t>
         </is>
       </c>
       <c r="F53" s="7" t="inlineStr">
         <is>
-          <t>ห้องน้ำ / Self-care</t>
+          <t>ห้องทำงาน / รถยนต์</t>
         </is>
       </c>
       <c r="G53" s="7" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H53" s="7" t="inlineStr">
         <is>
-          <t>Education / Explainer</t>
+          <t>Proof (UGC / testimonial / demo)</t>
         </is>
       </c>
       <c r="I53" s="7" t="inlineStr">
         <is>
-          <t>Lemon8</t>
+          <t>FB / IG</t>
         </is>
       </c>
       <c r="J53" s="7" t="inlineStr">
         <is>
-          <t>Water heater</t>
+          <t>Health pillow</t>
         </is>
       </c>
       <c r="K53" s="7" t="inlineStr">
         <is>
-          <t>FELIX / LUKA / ELKA</t>
+          <t>เบาะรองหลัง / หมอนรองคอสำหรับรถยนต์</t>
         </is>
       </c>
       <c r="L53" s="7" t="inlineStr">
         <is>
-          <t>เลือกกำลังวัตต์ให้เหมาะกับบ้าน</t>
+          <t>Story "พ่อขับรถทุกวัน"</t>
         </is>
       </c>
       <c r="M53" s="8" t="n"/>
@@ -4706,69 +4726,69 @@
       </c>
       <c r="P53" s="7" t="inlineStr">
         <is>
-          <t>Beauty sub-brand ใช้ logo Beauty / ELCB: ยืนยันรุ่นที่มีก่อนโพส</t>
+          <t>5 ธ.ค. วันพ่อ: tone อบอุ่น ไม่ hard sell</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="11" t="inlineStr">
-        <is>
-          <t>W12</t>
+      <c r="A54" s="10" t="inlineStr">
+        <is>
+          <t>W10</t>
         </is>
       </c>
       <c r="B54" s="7" t="inlineStr">
         <is>
-          <t>14-20 ธ.ค.</t>
+          <t>30 พ.ย.-6 ธ.ค.</t>
         </is>
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
-          <t>ธ.ค. BOFU: ใบสั่งยาสำหรับบ้าน (Home Prescription)</t>
+          <t>พ.ย. MOFU: ผลตรวจรายห้อง</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>BOFU</t>
+          <t>MOFU</t>
         </is>
       </c>
       <c r="E54" s="7" t="inlineStr">
         <is>
-          <t>Gift of Wellness + ห้องน้ำหน้าหนาว</t>
+          <t>ของขวัญดูแลพ่อ</t>
         </is>
       </c>
       <c r="F54" s="7" t="inlineStr">
         <is>
-          <t>ห้องน้ำ / Self-care</t>
+          <t>ห้องทำงาน / รถยนต์</t>
         </is>
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H54" s="7" t="inlineStr">
         <is>
-          <t>Proof (UGC / testimonial / demo)</t>
+          <t>Short video (hook 3 วิ)</t>
         </is>
       </c>
       <c r="I54" s="7" t="inlineStr">
         <is>
-          <t>IG</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="J54" s="7" t="inlineStr">
         <is>
-          <t>Hair styling</t>
+          <t>Air purifier</t>
         </is>
       </c>
       <c r="K54" s="7" t="inlineStr">
         <is>
-          <t>เครื่องหนีบผม 23 / 40 มม.</t>
+          <t>เครื่องฟอกอากาศในรถยนต์</t>
         </is>
       </c>
       <c r="L54" s="7" t="inlineStr">
         <is>
-          <t>Unboxing gift set</t>
+          <t>อากาศในรถที่พ่อนั่งทุกวัน</t>
         </is>
       </c>
       <c r="M54" s="8" t="n"/>
@@ -4780,54 +4800,54 @@
       </c>
       <c r="P54" s="7" t="inlineStr">
         <is>
-          <t>Beauty sub-brand ใช้ logo Beauty / ELCB: ยืนยันรุ่นที่มีก่อนโพส</t>
+          <t>5 ธ.ค. วันพ่อ: tone อบอุ่น ไม่ hard sell</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="11" t="inlineStr">
-        <is>
-          <t>W12</t>
+      <c r="A55" s="10" t="inlineStr">
+        <is>
+          <t>W10</t>
         </is>
       </c>
       <c r="B55" s="7" t="inlineStr">
         <is>
-          <t>14-20 ธ.ค.</t>
+          <t>30 พ.ย.-6 ธ.ค.</t>
         </is>
       </c>
       <c r="C55" s="7" t="inlineStr">
         <is>
-          <t>ธ.ค. BOFU: ใบสั่งยาสำหรับบ้าน (Home Prescription)</t>
+          <t>พ.ย. MOFU: ผลตรวจรายห้อง</t>
         </is>
       </c>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t>BOFU</t>
+          <t>MOFU</t>
         </is>
       </c>
       <c r="E55" s="7" t="inlineStr">
         <is>
-          <t>Gift of Wellness + ห้องน้ำหน้าหนาว</t>
+          <t>ของขวัญดูแลพ่อ</t>
         </is>
       </c>
       <c r="F55" s="7" t="inlineStr">
         <is>
-          <t>ห้องน้ำ / Self-care</t>
+          <t>ห้องทำงาน / รถยนต์</t>
         </is>
       </c>
       <c r="G55" s="7" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="H55" s="7" t="inlineStr">
         <is>
-          <t>LINE OA broadcast</t>
+          <t>Engagement (poll / quiz CTA / Q&amp;A)</t>
         </is>
       </c>
       <c r="I55" s="7" t="inlineStr">
         <is>
-          <t>LINE OA</t>
+          <t>FB</t>
         </is>
       </c>
       <c r="J55" s="7" t="inlineStr">
@@ -4842,7 +4862,7 @@
       </c>
       <c r="L55" s="7" t="inlineStr">
         <is>
-          <t>Gift guide ตาม persona + corporate gift [ถ้ามี]</t>
+          <t>"พ่อคุณปวดหลังไหม" poll</t>
         </is>
       </c>
       <c r="M55" s="8" t="n"/>
@@ -4852,67 +4872,71 @@
           <t>Not started</t>
         </is>
       </c>
-      <c r="P55" s="7" t="inlineStr"/>
+      <c r="P55" s="7" t="inlineStr">
+        <is>
+          <t>5 ธ.ค. วันพ่อ: tone อบอุ่น ไม่ hard sell</t>
+        </is>
+      </c>
     </row>
     <row r="56">
-      <c r="A56" s="11" t="inlineStr">
-        <is>
-          <t>W13</t>
+      <c r="A56" s="10" t="inlineStr">
+        <is>
+          <t>W10</t>
         </is>
       </c>
       <c r="B56" s="7" t="inlineStr">
         <is>
-          <t>21-27 ธ.ค.</t>
+          <t>30 พ.ย.-6 ธ.ค.</t>
         </is>
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
-          <t>ธ.ค. BOFU: ใบสั่งยาสำหรับบ้าน (Home Prescription)</t>
+          <t>พ.ย. MOFU: ผลตรวจรายห้อง</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>BOFU</t>
+          <t>MOFU</t>
         </is>
       </c>
       <c r="E56" s="7" t="inlineStr">
         <is>
-          <t>Party Season</t>
+          <t>ของขวัญดูแลพ่อ</t>
         </is>
       </c>
       <c r="F56" s="7" t="inlineStr">
         <is>
-          <t>ห้องนั่งเล่น / Self-care</t>
+          <t>ห้องทำงาน / รถยนต์</t>
         </is>
       </c>
       <c r="G56" s="7" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>E</t>
         </is>
       </c>
       <c r="H56" s="7" t="inlineStr">
         <is>
-          <t>Short video (hook 3 วิ)</t>
+          <t>LINE OA broadcast</t>
         </is>
       </c>
       <c r="I56" s="7" t="inlineStr">
         <is>
-          <t>TikTok / Reels</t>
+          <t>LINE OA</t>
         </is>
       </c>
       <c r="J56" s="7" t="inlineStr">
         <is>
-          <t>Robot vacuum</t>
+          <t>Cross-category</t>
         </is>
       </c>
       <c r="K56" s="7" t="inlineStr">
         <is>
-          <t>L6C / L0 / Y1 / Ultra T20</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L56" s="7" t="inlineStr">
         <is>
-          <t>"หลังปาร์ตี้ บ้านสะอาดเอง"</t>
+          <t>Father's Day gift guide</t>
         </is>
       </c>
       <c r="M56" s="8" t="n"/>
@@ -4922,21 +4946,17 @@
           <t>Not started</t>
         </is>
       </c>
-      <c r="P56" s="7" t="inlineStr">
-        <is>
-          <t>Christmas</t>
-        </is>
-      </c>
+      <c r="P56" s="7" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="11" t="inlineStr">
         <is>
-          <t>W13</t>
+          <t>W11</t>
         </is>
       </c>
       <c r="B57" s="7" t="inlineStr">
         <is>
-          <t>21-27 ธ.ค.</t>
+          <t>7-13 ธ.ค.</t>
         </is>
       </c>
       <c r="C57" s="7" t="inlineStr">
@@ -4951,42 +4971,42 @@
       </c>
       <c r="E57" s="7" t="inlineStr">
         <is>
-          <t>Party Season</t>
+          <t>12.12 Home Prescription</t>
         </is>
       </c>
       <c r="F57" s="7" t="inlineStr">
         <is>
-          <t>ห้องนั่งเล่น / Self-care</t>
+          <t>ทั้งบ้าน</t>
         </is>
       </c>
       <c r="G57" s="7" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H57" s="7" t="inlineStr">
         <is>
-          <t>Proof (UGC / testimonial / demo)</t>
+          <t>Education / Explainer</t>
         </is>
       </c>
       <c r="I57" s="7" t="inlineStr">
         <is>
-          <t>IG / TikTok</t>
+          <t>FB / IG</t>
         </is>
       </c>
       <c r="J57" s="7" t="inlineStr">
         <is>
-          <t>Hair styling</t>
+          <t>Cross-category</t>
         </is>
       </c>
       <c r="K57" s="7" t="inlineStr">
         <is>
-          <t>เครื่องหนีบผมลมร้อน</t>
+          <t>Bedroom: AP-8119US + หมอนรองคอ</t>
         </is>
       </c>
       <c r="L57" s="7" t="inlineStr">
         <is>
-          <t>UGC จัดทรงไปงาน</t>
+          <t>"ใบสั่งยาห้องนอน" (bundle proposal)</t>
         </is>
       </c>
       <c r="M57" s="8" t="n"/>
@@ -4998,19 +5018,19 @@
       </c>
       <c r="P57" s="7" t="inlineStr">
         <is>
-          <t>Christmas</t>
+          <t>12.12 (ส.), 10 ธ.ค. วันหยุด / bundle เป็น proposal รอ confirm offer</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="11" t="inlineStr">
         <is>
-          <t>W13</t>
+          <t>W11</t>
         </is>
       </c>
       <c r="B58" s="7" t="inlineStr">
         <is>
-          <t>21-27 ธ.ค.</t>
+          <t>7-13 ธ.ค.</t>
         </is>
       </c>
       <c r="C58" s="7" t="inlineStr">
@@ -5025,22 +5045,22 @@
       </c>
       <c r="E58" s="7" t="inlineStr">
         <is>
-          <t>Party Season</t>
+          <t>12.12 Home Prescription</t>
         </is>
       </c>
       <c r="F58" s="7" t="inlineStr">
         <is>
-          <t>ห้องนั่งเล่น / Self-care</t>
+          <t>ทั้งบ้าน</t>
         </is>
       </c>
       <c r="G58" s="7" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H58" s="7" t="inlineStr">
         <is>
-          <t>Engagement (poll / quiz CTA / Q&amp;A)</t>
+          <t>Education / Explainer</t>
         </is>
       </c>
       <c r="I58" s="7" t="inlineStr">
@@ -5055,12 +5075,12 @@
       </c>
       <c r="K58" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Family: CF-8428 + RO แบบไร้ถัง</t>
         </is>
       </c>
       <c r="L58" s="7" t="inlineStr">
         <is>
-          <t>"ปีนี้บ้านคุณได้กี่คะแนน"</t>
+          <t>"ใบสั่งยาบ้านมีเด็ก" (bundle proposal)</t>
         </is>
       </c>
       <c r="M58" s="8" t="n"/>
@@ -5072,19 +5092,19 @@
       </c>
       <c r="P58" s="7" t="inlineStr">
         <is>
-          <t>Christmas</t>
+          <t>12.12 (ส.), 10 ธ.ค. วันหยุด / bundle เป็น proposal รอ confirm offer</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="11" t="inlineStr">
         <is>
-          <t>W13</t>
+          <t>W11</t>
         </is>
       </c>
       <c r="B59" s="7" t="inlineStr">
         <is>
-          <t>21-27 ธ.ค.</t>
+          <t>7-13 ธ.ค.</t>
         </is>
       </c>
       <c r="C59" s="7" t="inlineStr">
@@ -5099,27 +5119,27 @@
       </c>
       <c r="E59" s="7" t="inlineStr">
         <is>
-          <t>Party Season</t>
+          <t>12.12 Home Prescription</t>
         </is>
       </c>
       <c r="F59" s="7" t="inlineStr">
         <is>
-          <t>ห้องนั่งเล่น / Self-care</t>
+          <t>ทั้งบ้าน</t>
         </is>
       </c>
       <c r="G59" s="7" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H59" s="7" t="inlineStr">
         <is>
-          <t>LINE OA broadcast</t>
+          <t>Short video (hook 3 วิ)</t>
         </is>
       </c>
       <c r="I59" s="7" t="inlineStr">
         <is>
-          <t>LINE OA</t>
+          <t>TikTok / Reels</t>
         </is>
       </c>
       <c r="J59" s="7" t="inlineStr">
@@ -5134,7 +5154,7 @@
       </c>
       <c r="L59" s="7" t="inlineStr">
         <is>
-          <t>Year-end Thank You ถึงลูกค้าเดิม + privilege [ ]</t>
+          <t>12.12 countdown</t>
         </is>
       </c>
       <c r="M59" s="8" t="n"/>
@@ -5144,17 +5164,21 @@
           <t>Not started</t>
         </is>
       </c>
-      <c r="P59" s="7" t="inlineStr"/>
+      <c r="P59" s="7" t="inlineStr">
+        <is>
+          <t>12.12 (ส.), 10 ธ.ค. วันหยุด / bundle เป็น proposal รอ confirm offer</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="11" t="inlineStr">
         <is>
-          <t>W14</t>
+          <t>W11</t>
         </is>
       </c>
       <c r="B60" s="7" t="inlineStr">
         <is>
-          <t>28 ธ.ค.-3 ม.ค.</t>
+          <t>7-13 ธ.ค.</t>
         </is>
       </c>
       <c r="C60" s="7" t="inlineStr">
@@ -5169,7 +5193,7 @@
       </c>
       <c r="E60" s="7" t="inlineStr">
         <is>
-          <t>New Year Reset</t>
+          <t>12.12 Home Prescription</t>
         </is>
       </c>
       <c r="F60" s="7" t="inlineStr">
@@ -5179,32 +5203,32 @@
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H60" s="7" t="inlineStr">
         <is>
-          <t>Short video (hook 3 วิ)</t>
+          <t>Proof (UGC / testimonial / demo)</t>
         </is>
       </c>
       <c r="I60" s="7" t="inlineStr">
         <is>
-          <t>TikTok / Reels</t>
+          <t>Meta retargeting</t>
         </is>
       </c>
       <c r="J60" s="7" t="inlineStr">
         <is>
-          <t>Fitness</t>
+          <t>Cross-category</t>
         </is>
       </c>
       <c r="K60" s="7" t="inlineStr">
         <is>
-          <t>เสื่อโยคะ 12 มม. / Foam Roller</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L60" s="7" t="inlineStr">
         <is>
-          <t>"เริ่มปีใหม่ที่บ้าน ไม่ต้องรอ resolution"</t>
+          <t>Retarget คนที่ทำ quiz แล้ว ตามผล Home Score</t>
         </is>
       </c>
       <c r="M60" s="8" t="n"/>
@@ -5216,19 +5240,19 @@
       </c>
       <c r="P60" s="7" t="inlineStr">
         <is>
-          <t>31 ธ.ค.-1 ม.ค. greeting เท่านั้น</t>
+          <t>12.12 (ส.), 10 ธ.ค. วันหยุด / bundle เป็น proposal รอ confirm offer</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="11" t="inlineStr">
         <is>
-          <t>W14</t>
+          <t>W11</t>
         </is>
       </c>
       <c r="B61" s="7" t="inlineStr">
         <is>
-          <t>28 ธ.ค.-3 ม.ค.</t>
+          <t>7-13 ธ.ค.</t>
         </is>
       </c>
       <c r="C61" s="7" t="inlineStr">
@@ -5243,7 +5267,7 @@
       </c>
       <c r="E61" s="7" t="inlineStr">
         <is>
-          <t>New Year Reset</t>
+          <t>12.12 Home Prescription</t>
         </is>
       </c>
       <c r="F61" s="7" t="inlineStr">
@@ -5253,32 +5277,32 @@
       </c>
       <c r="G61" s="7" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="H61" s="7" t="inlineStr">
         <is>
-          <t>Education / Explainer</t>
+          <t>Seasonal (ผูกฤดูกาล)</t>
         </is>
       </c>
       <c r="I61" s="7" t="inlineStr">
         <is>
-          <t>FB / IG</t>
+          <t>IG / FB</t>
         </is>
       </c>
       <c r="J61" s="7" t="inlineStr">
         <is>
-          <t>Cross-category</t>
+          <t>Health pillow</t>
         </is>
       </c>
       <c r="K61" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>หมอนรองคอเพื่อสุขภาพ</t>
         </is>
       </c>
       <c r="L61" s="7" t="inlineStr">
         <is>
-          <t>Home Score 2027 checklist</t>
+          <t>[หนาว] คืนอากาศเย็น: "หนาวนี้นอนดีขึ้นได้อีก"</t>
         </is>
       </c>
       <c r="M61" s="8" t="n"/>
@@ -5290,19 +5314,19 @@
       </c>
       <c r="P61" s="7" t="inlineStr">
         <is>
-          <t>31 ธ.ค.-1 ม.ค. greeting เท่านั้น</t>
+          <t>12.12 (ส.), 10 ธ.ค. วันหยุด / bundle เป็น proposal รอ confirm offer</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="11" t="inlineStr">
         <is>
-          <t>W14</t>
+          <t>W11</t>
         </is>
       </c>
       <c r="B62" s="7" t="inlineStr">
         <is>
-          <t>28 ธ.ค.-3 ม.ค.</t>
+          <t>7-13 ธ.ค.</t>
         </is>
       </c>
       <c r="C62" s="7" t="inlineStr">
@@ -5317,7 +5341,7 @@
       </c>
       <c r="E62" s="7" t="inlineStr">
         <is>
-          <t>New Year Reset</t>
+          <t>12.12 Home Prescription</t>
         </is>
       </c>
       <c r="F62" s="7" t="inlineStr">
@@ -5327,32 +5351,32 @@
       </c>
       <c r="G62" s="7" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>E</t>
         </is>
       </c>
       <c r="H62" s="7" t="inlineStr">
         <is>
-          <t>Education / Explainer</t>
+          <t>LINE OA broadcast</t>
         </is>
       </c>
       <c r="I62" s="7" t="inlineStr">
         <is>
-          <t>FB</t>
+          <t>LINE OA</t>
         </is>
       </c>
       <c r="J62" s="7" t="inlineStr">
         <is>
-          <t>Water heater</t>
+          <t>Cross-category</t>
         </is>
       </c>
       <c r="K62" s="7" t="inlineStr">
         <is>
-          <t>FELIX</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L62" s="7" t="inlineStr">
         <is>
-          <t>อาบน้ำอุ่นรับปีใหม่ เช็คความปลอดภัยก่อนใช้</t>
+          <t>Prescription bundle ตาม tag + 12.12 offer [ ]</t>
         </is>
       </c>
       <c r="M62" s="8" t="n"/>
@@ -5362,21 +5386,17 @@
           <t>Not started</t>
         </is>
       </c>
-      <c r="P62" s="7" t="inlineStr">
-        <is>
-          <t>31 ธ.ค.-1 ม.ค. greeting เท่านั้น</t>
-        </is>
-      </c>
+      <c r="P62" s="7" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="11" t="inlineStr">
         <is>
-          <t>W14</t>
+          <t>W12</t>
         </is>
       </c>
       <c r="B63" s="7" t="inlineStr">
         <is>
-          <t>28 ธ.ค.-3 ม.ค.</t>
+          <t>14-20 ธ.ค.</t>
         </is>
       </c>
       <c r="C63" s="7" t="inlineStr">
@@ -5391,42 +5411,42 @@
       </c>
       <c r="E63" s="7" t="inlineStr">
         <is>
-          <t>New Year Reset</t>
+          <t>Gift of Wellness + ห้องน้ำหน้าหนาว</t>
         </is>
       </c>
       <c r="F63" s="7" t="inlineStr">
         <is>
-          <t>ทั้งบ้าน</t>
+          <t>ห้องน้ำ / Self-care</t>
         </is>
       </c>
       <c r="G63" s="7" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H63" s="7" t="inlineStr">
         <is>
-          <t>Education / Explainer</t>
+          <t>Short video (hook 3 วิ)</t>
         </is>
       </c>
       <c r="I63" s="7" t="inlineStr">
         <is>
-          <t>FB / IG</t>
+          <t>TikTok / IG</t>
         </is>
       </c>
       <c r="J63" s="7" t="inlineStr">
         <is>
-          <t>Cross-category</t>
+          <t>Hair styling</t>
         </is>
       </c>
       <c r="K63" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>BSL-01 / BSL-02</t>
         </is>
       </c>
       <c r="L63" s="7" t="inlineStr">
         <is>
-          <t>Recap campaign</t>
+          <t>GRWM "ช่วงปาร์ตี้ จัดทรงทุกวันแต่ผมไม่เสีย"</t>
         </is>
       </c>
       <c r="M63" s="8" t="n"/>
@@ -5438,19 +5458,19 @@
       </c>
       <c r="P63" s="7" t="inlineStr">
         <is>
-          <t>31 ธ.ค.-1 ม.ค. greeting เท่านั้น</t>
+          <t>Beauty sub-brand ใช้ logo Beauty / ELCB: ยืนยันรุ่นที่มีก่อนโพส</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="11" t="inlineStr">
         <is>
-          <t>W14</t>
+          <t>W12</t>
         </is>
       </c>
       <c r="B64" s="7" t="inlineStr">
         <is>
-          <t>28 ธ.ค.-3 ม.ค.</t>
+          <t>14-20 ธ.ค.</t>
         </is>
       </c>
       <c r="C64" s="7" t="inlineStr">
@@ -5465,42 +5485,42 @@
       </c>
       <c r="E64" s="7" t="inlineStr">
         <is>
-          <t>New Year Reset</t>
+          <t>Gift of Wellness + ห้องน้ำหน้าหนาว</t>
         </is>
       </c>
       <c r="F64" s="7" t="inlineStr">
         <is>
-          <t>ทั้งบ้าน</t>
+          <t>ห้องน้ำ / Self-care</t>
         </is>
       </c>
       <c r="G64" s="7" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H64" s="7" t="inlineStr">
         <is>
-          <t>LINE OA broadcast</t>
+          <t>Education / Explainer</t>
         </is>
       </c>
       <c r="I64" s="7" t="inlineStr">
         <is>
-          <t>LINE OA</t>
+          <t>FB / IG</t>
         </is>
       </c>
       <c r="J64" s="7" t="inlineStr">
         <is>
-          <t>Cross-category</t>
+          <t>Water heater</t>
         </is>
       </c>
       <c r="K64" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>FELIX / LUKA / ELKA / Konrad</t>
         </is>
       </c>
       <c r="L64" s="7" t="inlineStr">
         <is>
-          <t>Filter Reminder + ชวนทำ quiz ใหม่ปี 2027</t>
+          <t>"ลมหนาวมาแล้ว ห้องน้ำบ้านคุณปลอดภัยไหม" (ระบบตัดไฟ ELCB)</t>
         </is>
       </c>
       <c r="M64" s="8" t="n"/>
@@ -5510,12 +5530,1114 @@
           <t>Not started</t>
         </is>
       </c>
-      <c r="P64" s="7" t="inlineStr"/>
+      <c r="P64" s="7" t="inlineStr">
+        <is>
+          <t>Beauty sub-brand ใช้ logo Beauty / ELCB: ยืนยันรุ่นที่มีก่อนโพส</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="11" t="inlineStr">
+        <is>
+          <t>W12</t>
+        </is>
+      </c>
+      <c r="B65" s="7" t="inlineStr">
+        <is>
+          <t>14-20 ธ.ค.</t>
+        </is>
+      </c>
+      <c r="C65" s="7" t="inlineStr">
+        <is>
+          <t>ธ.ค. BOFU: ใบสั่งยาสำหรับบ้าน (Home Prescription)</t>
+        </is>
+      </c>
+      <c r="D65" s="7" t="inlineStr">
+        <is>
+          <t>BOFU</t>
+        </is>
+      </c>
+      <c r="E65" s="7" t="inlineStr">
+        <is>
+          <t>Gift of Wellness + ห้องน้ำหน้าหนาว</t>
+        </is>
+      </c>
+      <c r="F65" s="7" t="inlineStr">
+        <is>
+          <t>ห้องน้ำ / Self-care</t>
+        </is>
+      </c>
+      <c r="G65" s="7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H65" s="7" t="inlineStr">
+        <is>
+          <t>Education / Explainer</t>
+        </is>
+      </c>
+      <c r="I65" s="7" t="inlineStr">
+        <is>
+          <t>Lemon8</t>
+        </is>
+      </c>
+      <c r="J65" s="7" t="inlineStr">
+        <is>
+          <t>Water heater</t>
+        </is>
+      </c>
+      <c r="K65" s="7" t="inlineStr">
+        <is>
+          <t>FELIX / LUKA / ELKA</t>
+        </is>
+      </c>
+      <c r="L65" s="7" t="inlineStr">
+        <is>
+          <t>เลือกกำลังวัตต์ให้เหมาะกับบ้าน</t>
+        </is>
+      </c>
+      <c r="M65" s="8" t="n"/>
+      <c r="N65" s="9" t="n"/>
+      <c r="O65" s="8" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="P65" s="7" t="inlineStr">
+        <is>
+          <t>Beauty sub-brand ใช้ logo Beauty / ELCB: ยืนยันรุ่นที่มีก่อนโพส</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="11" t="inlineStr">
+        <is>
+          <t>W12</t>
+        </is>
+      </c>
+      <c r="B66" s="7" t="inlineStr">
+        <is>
+          <t>14-20 ธ.ค.</t>
+        </is>
+      </c>
+      <c r="C66" s="7" t="inlineStr">
+        <is>
+          <t>ธ.ค. BOFU: ใบสั่งยาสำหรับบ้าน (Home Prescription)</t>
+        </is>
+      </c>
+      <c r="D66" s="7" t="inlineStr">
+        <is>
+          <t>BOFU</t>
+        </is>
+      </c>
+      <c r="E66" s="7" t="inlineStr">
+        <is>
+          <t>Gift of Wellness + ห้องน้ำหน้าหนาว</t>
+        </is>
+      </c>
+      <c r="F66" s="7" t="inlineStr">
+        <is>
+          <t>ห้องน้ำ / Self-care</t>
+        </is>
+      </c>
+      <c r="G66" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H66" s="7" t="inlineStr">
+        <is>
+          <t>Proof (UGC / testimonial / demo)</t>
+        </is>
+      </c>
+      <c r="I66" s="7" t="inlineStr">
+        <is>
+          <t>IG</t>
+        </is>
+      </c>
+      <c r="J66" s="7" t="inlineStr">
+        <is>
+          <t>Hair styling</t>
+        </is>
+      </c>
+      <c r="K66" s="7" t="inlineStr">
+        <is>
+          <t>เครื่องหนีบผม 23 / 40 มม.</t>
+        </is>
+      </c>
+      <c r="L66" s="7" t="inlineStr">
+        <is>
+          <t>Unboxing gift set</t>
+        </is>
+      </c>
+      <c r="M66" s="8" t="n"/>
+      <c r="N66" s="9" t="n"/>
+      <c r="O66" s="8" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="P66" s="7" t="inlineStr">
+        <is>
+          <t>Beauty sub-brand ใช้ logo Beauty / ELCB: ยืนยันรุ่นที่มีก่อนโพส</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="11" t="inlineStr">
+        <is>
+          <t>W12</t>
+        </is>
+      </c>
+      <c r="B67" s="7" t="inlineStr">
+        <is>
+          <t>14-20 ธ.ค.</t>
+        </is>
+      </c>
+      <c r="C67" s="7" t="inlineStr">
+        <is>
+          <t>ธ.ค. BOFU: ใบสั่งยาสำหรับบ้าน (Home Prescription)</t>
+        </is>
+      </c>
+      <c r="D67" s="7" t="inlineStr">
+        <is>
+          <t>BOFU</t>
+        </is>
+      </c>
+      <c r="E67" s="7" t="inlineStr">
+        <is>
+          <t>Gift of Wellness + ห้องน้ำหน้าหนาว</t>
+        </is>
+      </c>
+      <c r="F67" s="7" t="inlineStr">
+        <is>
+          <t>ห้องน้ำ / Self-care</t>
+        </is>
+      </c>
+      <c r="G67" s="7" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="H67" s="7" t="inlineStr">
+        <is>
+          <t>Seasonal (ผูกฤดูกาล)</t>
+        </is>
+      </c>
+      <c r="I67" s="7" t="inlineStr">
+        <is>
+          <t>FB</t>
+        </is>
+      </c>
+      <c r="J67" s="7" t="inlineStr">
+        <is>
+          <t>Water heater</t>
+        </is>
+      </c>
+      <c r="K67" s="7" t="inlineStr">
+        <is>
+          <t>FELIX / LUKA / ELKA</t>
+        </is>
+      </c>
+      <c r="L67" s="7" t="inlineStr">
+        <is>
+          <t>[หนาว] ของขวัญบ้านพ่อแม่ต่างจังหวัด: "บ้านพ่อแม่หนาวกว่ากรุงเทพฯ"</t>
+        </is>
+      </c>
+      <c r="M67" s="8" t="n"/>
+      <c r="N67" s="9" t="n"/>
+      <c r="O67" s="8" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="P67" s="7" t="inlineStr">
+        <is>
+          <t>Beauty sub-brand ใช้ logo Beauty / ELCB: ยืนยันรุ่นที่มีก่อนโพส</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="11" t="inlineStr">
+        <is>
+          <t>W12</t>
+        </is>
+      </c>
+      <c r="B68" s="7" t="inlineStr">
+        <is>
+          <t>14-20 ธ.ค.</t>
+        </is>
+      </c>
+      <c r="C68" s="7" t="inlineStr">
+        <is>
+          <t>ธ.ค. BOFU: ใบสั่งยาสำหรับบ้าน (Home Prescription)</t>
+        </is>
+      </c>
+      <c r="D68" s="7" t="inlineStr">
+        <is>
+          <t>BOFU</t>
+        </is>
+      </c>
+      <c r="E68" s="7" t="inlineStr">
+        <is>
+          <t>Gift of Wellness + ห้องน้ำหน้าหนาว</t>
+        </is>
+      </c>
+      <c r="F68" s="7" t="inlineStr">
+        <is>
+          <t>ห้องน้ำ / Self-care</t>
+        </is>
+      </c>
+      <c r="G68" s="7" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="H68" s="7" t="inlineStr">
+        <is>
+          <t>Seasonal (ผูกฤดูกาล)</t>
+        </is>
+      </c>
+      <c r="I68" s="7" t="inlineStr">
+        <is>
+          <t>TikTok / IG</t>
+        </is>
+      </c>
+      <c r="J68" s="7" t="inlineStr">
+        <is>
+          <t>Hair styling</t>
+        </is>
+      </c>
+      <c r="K68" s="7" t="inlineStr">
+        <is>
+          <t>BSL-01 / BSL-02</t>
+        </is>
+      </c>
+      <c r="L68" s="7" t="inlineStr">
+        <is>
+          <t>[หนาว] อากาศแห้ง ผมชี้ฟู: "ลมหนาวมา ผมจัดทรงยากขึ้น"</t>
+        </is>
+      </c>
+      <c r="M68" s="8" t="n"/>
+      <c r="N68" s="9" t="n"/>
+      <c r="O68" s="8" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="P68" s="7" t="inlineStr">
+        <is>
+          <t>Beauty sub-brand ใช้ logo Beauty / ELCB: ยืนยันรุ่นที่มีก่อนโพส</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="11" t="inlineStr">
+        <is>
+          <t>W12</t>
+        </is>
+      </c>
+      <c r="B69" s="7" t="inlineStr">
+        <is>
+          <t>14-20 ธ.ค.</t>
+        </is>
+      </c>
+      <c r="C69" s="7" t="inlineStr">
+        <is>
+          <t>ธ.ค. BOFU: ใบสั่งยาสำหรับบ้าน (Home Prescription)</t>
+        </is>
+      </c>
+      <c r="D69" s="7" t="inlineStr">
+        <is>
+          <t>BOFU</t>
+        </is>
+      </c>
+      <c r="E69" s="7" t="inlineStr">
+        <is>
+          <t>Gift of Wellness + ห้องน้ำหน้าหนาว</t>
+        </is>
+      </c>
+      <c r="F69" s="7" t="inlineStr">
+        <is>
+          <t>ห้องน้ำ / Self-care</t>
+        </is>
+      </c>
+      <c r="G69" s="7" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="H69" s="7" t="inlineStr">
+        <is>
+          <t>LINE OA broadcast</t>
+        </is>
+      </c>
+      <c r="I69" s="7" t="inlineStr">
+        <is>
+          <t>LINE OA</t>
+        </is>
+      </c>
+      <c r="J69" s="7" t="inlineStr">
+        <is>
+          <t>Cross-category</t>
+        </is>
+      </c>
+      <c r="K69" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L69" s="7" t="inlineStr">
+        <is>
+          <t>Gift guide ตาม persona + corporate gift [ถ้ามี]</t>
+        </is>
+      </c>
+      <c r="M69" s="8" t="n"/>
+      <c r="N69" s="9" t="n"/>
+      <c r="O69" s="8" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="P69" s="7" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="11" t="inlineStr">
+        <is>
+          <t>W13</t>
+        </is>
+      </c>
+      <c r="B70" s="7" t="inlineStr">
+        <is>
+          <t>21-27 ธ.ค.</t>
+        </is>
+      </c>
+      <c r="C70" s="7" t="inlineStr">
+        <is>
+          <t>ธ.ค. BOFU: ใบสั่งยาสำหรับบ้าน (Home Prescription)</t>
+        </is>
+      </c>
+      <c r="D70" s="7" t="inlineStr">
+        <is>
+          <t>BOFU</t>
+        </is>
+      </c>
+      <c r="E70" s="7" t="inlineStr">
+        <is>
+          <t>Party Season</t>
+        </is>
+      </c>
+      <c r="F70" s="7" t="inlineStr">
+        <is>
+          <t>ห้องนั่งเล่น / Self-care</t>
+        </is>
+      </c>
+      <c r="G70" s="7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H70" s="7" t="inlineStr">
+        <is>
+          <t>Short video (hook 3 วิ)</t>
+        </is>
+      </c>
+      <c r="I70" s="7" t="inlineStr">
+        <is>
+          <t>TikTok / Reels</t>
+        </is>
+      </c>
+      <c r="J70" s="7" t="inlineStr">
+        <is>
+          <t>Robot vacuum</t>
+        </is>
+      </c>
+      <c r="K70" s="7" t="inlineStr">
+        <is>
+          <t>L6C / L0 / Y1 / Ultra T20</t>
+        </is>
+      </c>
+      <c r="L70" s="7" t="inlineStr">
+        <is>
+          <t>"หลังปาร์ตี้ บ้านสะอาดเอง"</t>
+        </is>
+      </c>
+      <c r="M70" s="8" t="n"/>
+      <c r="N70" s="9" t="n"/>
+      <c r="O70" s="8" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="P70" s="7" t="inlineStr">
+        <is>
+          <t>Christmas</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="11" t="inlineStr">
+        <is>
+          <t>W13</t>
+        </is>
+      </c>
+      <c r="B71" s="7" t="inlineStr">
+        <is>
+          <t>21-27 ธ.ค.</t>
+        </is>
+      </c>
+      <c r="C71" s="7" t="inlineStr">
+        <is>
+          <t>ธ.ค. BOFU: ใบสั่งยาสำหรับบ้าน (Home Prescription)</t>
+        </is>
+      </c>
+      <c r="D71" s="7" t="inlineStr">
+        <is>
+          <t>BOFU</t>
+        </is>
+      </c>
+      <c r="E71" s="7" t="inlineStr">
+        <is>
+          <t>Party Season</t>
+        </is>
+      </c>
+      <c r="F71" s="7" t="inlineStr">
+        <is>
+          <t>ห้องนั่งเล่น / Self-care</t>
+        </is>
+      </c>
+      <c r="G71" s="7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H71" s="7" t="inlineStr">
+        <is>
+          <t>Proof (UGC / testimonial / demo)</t>
+        </is>
+      </c>
+      <c r="I71" s="7" t="inlineStr">
+        <is>
+          <t>IG / TikTok</t>
+        </is>
+      </c>
+      <c r="J71" s="7" t="inlineStr">
+        <is>
+          <t>Hair styling</t>
+        </is>
+      </c>
+      <c r="K71" s="7" t="inlineStr">
+        <is>
+          <t>เครื่องหนีบผมลมร้อน</t>
+        </is>
+      </c>
+      <c r="L71" s="7" t="inlineStr">
+        <is>
+          <t>UGC จัดทรงไปงาน</t>
+        </is>
+      </c>
+      <c r="M71" s="8" t="n"/>
+      <c r="N71" s="9" t="n"/>
+      <c r="O71" s="8" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="P71" s="7" t="inlineStr">
+        <is>
+          <t>Christmas</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="11" t="inlineStr">
+        <is>
+          <t>W13</t>
+        </is>
+      </c>
+      <c r="B72" s="7" t="inlineStr">
+        <is>
+          <t>21-27 ธ.ค.</t>
+        </is>
+      </c>
+      <c r="C72" s="7" t="inlineStr">
+        <is>
+          <t>ธ.ค. BOFU: ใบสั่งยาสำหรับบ้าน (Home Prescription)</t>
+        </is>
+      </c>
+      <c r="D72" s="7" t="inlineStr">
+        <is>
+          <t>BOFU</t>
+        </is>
+      </c>
+      <c r="E72" s="7" t="inlineStr">
+        <is>
+          <t>Party Season</t>
+        </is>
+      </c>
+      <c r="F72" s="7" t="inlineStr">
+        <is>
+          <t>ห้องนั่งเล่น / Self-care</t>
+        </is>
+      </c>
+      <c r="G72" s="7" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H72" s="7" t="inlineStr">
+        <is>
+          <t>Engagement (poll / quiz CTA / Q&amp;A)</t>
+        </is>
+      </c>
+      <c r="I72" s="7" t="inlineStr">
+        <is>
+          <t>FB / IG</t>
+        </is>
+      </c>
+      <c r="J72" s="7" t="inlineStr">
+        <is>
+          <t>Cross-category</t>
+        </is>
+      </c>
+      <c r="K72" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L72" s="7" t="inlineStr">
+        <is>
+          <t>"ปีนี้บ้านคุณได้กี่คะแนน"</t>
+        </is>
+      </c>
+      <c r="M72" s="8" t="n"/>
+      <c r="N72" s="9" t="n"/>
+      <c r="O72" s="8" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="P72" s="7" t="inlineStr">
+        <is>
+          <t>Christmas</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="11" t="inlineStr">
+        <is>
+          <t>W13</t>
+        </is>
+      </c>
+      <c r="B73" s="7" t="inlineStr">
+        <is>
+          <t>21-27 ธ.ค.</t>
+        </is>
+      </c>
+      <c r="C73" s="7" t="inlineStr">
+        <is>
+          <t>ธ.ค. BOFU: ใบสั่งยาสำหรับบ้าน (Home Prescription)</t>
+        </is>
+      </c>
+      <c r="D73" s="7" t="inlineStr">
+        <is>
+          <t>BOFU</t>
+        </is>
+      </c>
+      <c r="E73" s="7" t="inlineStr">
+        <is>
+          <t>Party Season</t>
+        </is>
+      </c>
+      <c r="F73" s="7" t="inlineStr">
+        <is>
+          <t>ห้องนั่งเล่น / Self-care</t>
+        </is>
+      </c>
+      <c r="G73" s="7" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="H73" s="7" t="inlineStr">
+        <is>
+          <t>Seasonal (ผูกฤดูกาล)</t>
+        </is>
+      </c>
+      <c r="I73" s="7" t="inlineStr">
+        <is>
+          <t>FB / IG</t>
+        </is>
+      </c>
+      <c r="J73" s="7" t="inlineStr">
+        <is>
+          <t>Health pillow</t>
+        </is>
+      </c>
+      <c r="K73" s="7" t="inlineStr">
+        <is>
+          <t>เบาะรองหลัง / หมอนรองคอสำหรับรถยนต์</t>
+        </is>
+      </c>
+      <c r="L73" s="7" t="inlineStr">
+        <is>
+          <t>[หนาว] เดินทางไกลช่วงปีใหม่: "เดินทางไกลช่วงปีใหม่ คอกับหลังพร้อมไหม"</t>
+        </is>
+      </c>
+      <c r="M73" s="8" t="n"/>
+      <c r="N73" s="9" t="n"/>
+      <c r="O73" s="8" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="P73" s="7" t="inlineStr">
+        <is>
+          <t>Christmas</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="11" t="inlineStr">
+        <is>
+          <t>W13</t>
+        </is>
+      </c>
+      <c r="B74" s="7" t="inlineStr">
+        <is>
+          <t>21-27 ธ.ค.</t>
+        </is>
+      </c>
+      <c r="C74" s="7" t="inlineStr">
+        <is>
+          <t>ธ.ค. BOFU: ใบสั่งยาสำหรับบ้าน (Home Prescription)</t>
+        </is>
+      </c>
+      <c r="D74" s="7" t="inlineStr">
+        <is>
+          <t>BOFU</t>
+        </is>
+      </c>
+      <c r="E74" s="7" t="inlineStr">
+        <is>
+          <t>Party Season</t>
+        </is>
+      </c>
+      <c r="F74" s="7" t="inlineStr">
+        <is>
+          <t>ห้องนั่งเล่น / Self-care</t>
+        </is>
+      </c>
+      <c r="G74" s="7" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="H74" s="7" t="inlineStr">
+        <is>
+          <t>LINE OA broadcast</t>
+        </is>
+      </c>
+      <c r="I74" s="7" t="inlineStr">
+        <is>
+          <t>LINE OA</t>
+        </is>
+      </c>
+      <c r="J74" s="7" t="inlineStr">
+        <is>
+          <t>Cross-category</t>
+        </is>
+      </c>
+      <c r="K74" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L74" s="7" t="inlineStr">
+        <is>
+          <t>Year-end Thank You ถึงลูกค้าเดิม + privilege [ ]</t>
+        </is>
+      </c>
+      <c r="M74" s="8" t="n"/>
+      <c r="N74" s="9" t="n"/>
+      <c r="O74" s="8" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="P74" s="7" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="11" t="inlineStr">
+        <is>
+          <t>W14</t>
+        </is>
+      </c>
+      <c r="B75" s="7" t="inlineStr">
+        <is>
+          <t>28 ธ.ค.-3 ม.ค.</t>
+        </is>
+      </c>
+      <c r="C75" s="7" t="inlineStr">
+        <is>
+          <t>ธ.ค. BOFU: ใบสั่งยาสำหรับบ้าน (Home Prescription)</t>
+        </is>
+      </c>
+      <c r="D75" s="7" t="inlineStr">
+        <is>
+          <t>BOFU</t>
+        </is>
+      </c>
+      <c r="E75" s="7" t="inlineStr">
+        <is>
+          <t>New Year Reset</t>
+        </is>
+      </c>
+      <c r="F75" s="7" t="inlineStr">
+        <is>
+          <t>ทั้งบ้าน</t>
+        </is>
+      </c>
+      <c r="G75" s="7" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H75" s="7" t="inlineStr">
+        <is>
+          <t>Short video (hook 3 วิ)</t>
+        </is>
+      </c>
+      <c r="I75" s="7" t="inlineStr">
+        <is>
+          <t>TikTok / Reels</t>
+        </is>
+      </c>
+      <c r="J75" s="7" t="inlineStr">
+        <is>
+          <t>Fitness</t>
+        </is>
+      </c>
+      <c r="K75" s="7" t="inlineStr">
+        <is>
+          <t>เสื่อโยคะ 12 มม. / Foam Roller</t>
+        </is>
+      </c>
+      <c r="L75" s="7" t="inlineStr">
+        <is>
+          <t>"เริ่มปีใหม่ที่บ้าน ไม่ต้องรอ resolution"</t>
+        </is>
+      </c>
+      <c r="M75" s="8" t="n"/>
+      <c r="N75" s="9" t="n"/>
+      <c r="O75" s="8" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="P75" s="7" t="inlineStr">
+        <is>
+          <t>31 ธ.ค.-1 ม.ค. greeting เท่านั้น</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="11" t="inlineStr">
+        <is>
+          <t>W14</t>
+        </is>
+      </c>
+      <c r="B76" s="7" t="inlineStr">
+        <is>
+          <t>28 ธ.ค.-3 ม.ค.</t>
+        </is>
+      </c>
+      <c r="C76" s="7" t="inlineStr">
+        <is>
+          <t>ธ.ค. BOFU: ใบสั่งยาสำหรับบ้าน (Home Prescription)</t>
+        </is>
+      </c>
+      <c r="D76" s="7" t="inlineStr">
+        <is>
+          <t>BOFU</t>
+        </is>
+      </c>
+      <c r="E76" s="7" t="inlineStr">
+        <is>
+          <t>New Year Reset</t>
+        </is>
+      </c>
+      <c r="F76" s="7" t="inlineStr">
+        <is>
+          <t>ทั้งบ้าน</t>
+        </is>
+      </c>
+      <c r="G76" s="7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H76" s="7" t="inlineStr">
+        <is>
+          <t>Education / Explainer</t>
+        </is>
+      </c>
+      <c r="I76" s="7" t="inlineStr">
+        <is>
+          <t>FB / IG</t>
+        </is>
+      </c>
+      <c r="J76" s="7" t="inlineStr">
+        <is>
+          <t>Cross-category</t>
+        </is>
+      </c>
+      <c r="K76" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L76" s="7" t="inlineStr">
+        <is>
+          <t>Home Score 2027 checklist</t>
+        </is>
+      </c>
+      <c r="M76" s="8" t="n"/>
+      <c r="N76" s="9" t="n"/>
+      <c r="O76" s="8" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="P76" s="7" t="inlineStr">
+        <is>
+          <t>31 ธ.ค.-1 ม.ค. greeting เท่านั้น</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="11" t="inlineStr">
+        <is>
+          <t>W14</t>
+        </is>
+      </c>
+      <c r="B77" s="7" t="inlineStr">
+        <is>
+          <t>28 ธ.ค.-3 ม.ค.</t>
+        </is>
+      </c>
+      <c r="C77" s="7" t="inlineStr">
+        <is>
+          <t>ธ.ค. BOFU: ใบสั่งยาสำหรับบ้าน (Home Prescription)</t>
+        </is>
+      </c>
+      <c r="D77" s="7" t="inlineStr">
+        <is>
+          <t>BOFU</t>
+        </is>
+      </c>
+      <c r="E77" s="7" t="inlineStr">
+        <is>
+          <t>New Year Reset</t>
+        </is>
+      </c>
+      <c r="F77" s="7" t="inlineStr">
+        <is>
+          <t>ทั้งบ้าน</t>
+        </is>
+      </c>
+      <c r="G77" s="7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H77" s="7" t="inlineStr">
+        <is>
+          <t>Education / Explainer</t>
+        </is>
+      </c>
+      <c r="I77" s="7" t="inlineStr">
+        <is>
+          <t>FB</t>
+        </is>
+      </c>
+      <c r="J77" s="7" t="inlineStr">
+        <is>
+          <t>Water heater</t>
+        </is>
+      </c>
+      <c r="K77" s="7" t="inlineStr">
+        <is>
+          <t>FELIX</t>
+        </is>
+      </c>
+      <c r="L77" s="7" t="inlineStr">
+        <is>
+          <t>อาบน้ำอุ่นรับปีใหม่ เช็คความปลอดภัยก่อนใช้</t>
+        </is>
+      </c>
+      <c r="M77" s="8" t="n"/>
+      <c r="N77" s="9" t="n"/>
+      <c r="O77" s="8" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="P77" s="7" t="inlineStr">
+        <is>
+          <t>31 ธ.ค.-1 ม.ค. greeting เท่านั้น</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="11" t="inlineStr">
+        <is>
+          <t>W14</t>
+        </is>
+      </c>
+      <c r="B78" s="7" t="inlineStr">
+        <is>
+          <t>28 ธ.ค.-3 ม.ค.</t>
+        </is>
+      </c>
+      <c r="C78" s="7" t="inlineStr">
+        <is>
+          <t>ธ.ค. BOFU: ใบสั่งยาสำหรับบ้าน (Home Prescription)</t>
+        </is>
+      </c>
+      <c r="D78" s="7" t="inlineStr">
+        <is>
+          <t>BOFU</t>
+        </is>
+      </c>
+      <c r="E78" s="7" t="inlineStr">
+        <is>
+          <t>New Year Reset</t>
+        </is>
+      </c>
+      <c r="F78" s="7" t="inlineStr">
+        <is>
+          <t>ทั้งบ้าน</t>
+        </is>
+      </c>
+      <c r="G78" s="7" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H78" s="7" t="inlineStr">
+        <is>
+          <t>Education / Explainer</t>
+        </is>
+      </c>
+      <c r="I78" s="7" t="inlineStr">
+        <is>
+          <t>FB / IG</t>
+        </is>
+      </c>
+      <c r="J78" s="7" t="inlineStr">
+        <is>
+          <t>Cross-category</t>
+        </is>
+      </c>
+      <c r="K78" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L78" s="7" t="inlineStr">
+        <is>
+          <t>Recap campaign</t>
+        </is>
+      </c>
+      <c r="M78" s="8" t="n"/>
+      <c r="N78" s="9" t="n"/>
+      <c r="O78" s="8" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="P78" s="7" t="inlineStr">
+        <is>
+          <t>31 ธ.ค.-1 ม.ค. greeting เท่านั้น</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="11" t="inlineStr">
+        <is>
+          <t>W14</t>
+        </is>
+      </c>
+      <c r="B79" s="7" t="inlineStr">
+        <is>
+          <t>28 ธ.ค.-3 ม.ค.</t>
+        </is>
+      </c>
+      <c r="C79" s="7" t="inlineStr">
+        <is>
+          <t>ธ.ค. BOFU: ใบสั่งยาสำหรับบ้าน (Home Prescription)</t>
+        </is>
+      </c>
+      <c r="D79" s="7" t="inlineStr">
+        <is>
+          <t>BOFU</t>
+        </is>
+      </c>
+      <c r="E79" s="7" t="inlineStr">
+        <is>
+          <t>New Year Reset</t>
+        </is>
+      </c>
+      <c r="F79" s="7" t="inlineStr">
+        <is>
+          <t>ทั้งบ้าน</t>
+        </is>
+      </c>
+      <c r="G79" s="7" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="H79" s="7" t="inlineStr">
+        <is>
+          <t>LINE OA broadcast</t>
+        </is>
+      </c>
+      <c r="I79" s="7" t="inlineStr">
+        <is>
+          <t>LINE OA</t>
+        </is>
+      </c>
+      <c r="J79" s="7" t="inlineStr">
+        <is>
+          <t>Cross-category</t>
+        </is>
+      </c>
+      <c r="K79" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L79" s="7" t="inlineStr">
+        <is>
+          <t>Filter Reminder + ชวนทำ quiz ใหม่ปี 2027</t>
+        </is>
+      </c>
+      <c r="M79" s="8" t="n"/>
+      <c r="N79" s="9" t="n"/>
+      <c r="O79" s="8" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="P79" s="7" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P64"/>
+  <autoFilter ref="A1:P79"/>
   <dataValidations count="1">
-    <dataValidation sqref="O2:O64" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="O2:O79" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Not started,Briefed,In production,Approved,Published"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5739,7 +6861,7 @@
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>Ergonomic chair, Health pillow</t>
+          <t>Cordless vacuum, Dehumidifier, Ergonomic chair, Health pillow</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr">
@@ -5781,7 +6903,7 @@
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>Air purifier, Water purifier</t>
+          <t>Air purifier, Portable AC, Water purifier</t>
         </is>
       </c>
       <c r="G6" s="7" t="inlineStr">
@@ -6033,7 +7155,7 @@
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>Cross-category</t>
+          <t>Health pillow</t>
         </is>
       </c>
       <c r="G12" s="7" t="inlineStr">
@@ -6117,7 +7239,7 @@
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>Hair styling, Robot vacuum</t>
+          <t>Hair styling, Health pillow, Robot vacuum</t>
         </is>
       </c>
       <c r="G14" s="7" t="inlineStr">
@@ -7264,7 +8386,7 @@
       </c>
       <c r="C3" s="7" t="inlineStr">
         <is>
-          <t>W2, W3</t>
+          <t>W2, W3, W4</t>
         </is>
       </c>
     </row>
@@ -7328,7 +8450,7 @@
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>W3, W9</t>
+          <t>W3, W4, W9</t>
         </is>
       </c>
     </row>
@@ -7344,7 +8466,7 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>W9</t>
+          <t>W5, W9</t>
         </is>
       </c>
     </row>
@@ -7376,7 +8498,7 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>W4, W6, W10</t>
+          <t>W4, W6, W10, W11, W13</t>
         </is>
       </c>
     </row>

--- a/campaign/2026-q4-home-checkup/Bwell_Q4-2026_Home-Checkup_Content-Calendar.xlsx
+++ b/campaign/2026-q4-home-checkup/Bwell_Q4-2026_Home-Checkup_Content-Calendar.xlsx
@@ -1481,7 +1481,7 @@
       </c>
       <c r="K9" s="7" t="inlineStr">
         <is>
-          <t>L6C / L0 / Y1</t>
+          <t>L6C</t>
         </is>
       </c>
       <c r="L9" s="7" t="inlineStr">
